--- a/tests/data/Methanex_tool_test_queries.xlsx
+++ b/tests/data/Methanex_tool_test_queries.xlsx
@@ -17751,7 +17751,7 @@
       </c>
       <c r="J2" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Курс рубля к доллару США в конце года (eop USD/RUB)", "Этилен, CFR Китай", "Нефть марки Brent", "Ключевая ставка на конец года (eop)"], "target_value": 1.85, "output_name": "Debt/EBITDA"}</t>
+          <t>{"input_names": ["Курс рубля к доллару США в конце года (eop USD/RUB)", "Этилен, CFR Китай", "Нефть марки Brent", "Ключевая ставка на конец года (eop)"], "target_value": 1.85, "output_name": "Debt/EBITDA", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -17797,7 +17797,7 @@
       </c>
       <c r="J3" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Карбамид (FOB Южный)", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": 3650, "output_name": "Выручка"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Карбамид (FOB Южный)", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": 3650, "output_name": "Выручка", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -17843,7 +17843,7 @@
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Hard Coking Coal (FOB Australia)", "Коэффициент цены", "Курс рубля к доллару США в конце года (eop USD/RUB)", "Никель (London Metals Exchange)", "Хлорид калия (CFR Ю-В Азия)"], "target_value": 5300, "output_name": "Выручка"}</t>
+          <t>{"input_names": ["Hard Coking Coal (FOB Australia)", "Коэффициент цены", "Курс рубля к доллару США в конце года (eop USD/RUB)", "Никель (London Metals Exchange)", "Хлорид калия (CFR Ю-В Азия)"], "target_value": 5300, "output_name": "Выручка", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Золото (London Metals Exchange)", "Коэффициент постоянных расходов", "Карбамид (FOB Южный)", "Коэффициент капитальных вложений"], "target_value": 750, "output_name": "Денежные средства, доступные для обслуживания долга (CFADS)"}</t>
+          <t>{"input_names": ["Золото (London Metals Exchange)", "Коэффициент постоянных расходов", "Карбамид (FOB Южный)", "Коэффициент капитальных вложений"], "target_value": 750, "output_name": "Денежные средства, доступные для обслуживания долга (CFADS)", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -17935,7 +17935,7 @@
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Коэффициент объема", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Аммиак (FOB Черное море)"], "target_value": -270, "output_name": "Денежные потоки от финансовых операций (CFF)"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Коэффициент объема", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Аммиак (FOB Черное море)"], "target_value": -270, "output_name": "Денежные потоки от финансовых операций (CFF)", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -17981,7 +17981,7 @@
       </c>
       <c r="J7" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Средний за период курс рубля к доллару США (av USD/RUB)", "Медь (London Metals Exchange)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Никель (London Metals Exchange)"], "target_value": 3.79, "output_name": "Минимальный годичный DSCR"}</t>
+          <t>{"input_names": ["Средний за период курс рубля к доллару США (av USD/RUB)", "Медь (London Metals Exchange)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Никель (London Metals Exchange)"], "target_value": 3.79, "output_name": "Минимальный годичный DSCR", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -18027,7 +18027,7 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Железная руда (Iron Ore 62%, CFR China)", "Цена на природный газ на хабе Henry Hub", "Медь (London Metals Exchange)", "Бензол, CFR Япония", "Цена урана"], "target_value": -250, "output_name": "Денежные потоки от финансовых операций (CFF)"}</t>
+          <t>{"input_names": ["Железная руда (Iron Ore 62%, CFR China)", "Цена на природный газ на хабе Henry Hub", "Медь (London Metals Exchange)", "Бензол, CFR Япония", "Цена урана"], "target_value": -250, "output_name": "Денежные потоки от финансовых операций (CFF)", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["ECB policy rate (Main Refinancing Operations rate)", "Метанол", "Курс рубля к EUR в конце года (eop EUR/RUB)"], "target_value": 140, "output_name": "Обслуживание долга (Debt Service)"}</t>
+          <t>{"input_names": ["ECB policy rate (Main Refinancing Operations rate)", "Метанол", "Курс рубля к EUR в конце года (eop EUR/RUB)"], "target_value": 140, "output_name": "Обслуживание долга (Debt Service)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -18119,7 +18119,7 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент капитальных вложений", "Рост реального ВВП", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Хлорид калия (CFR Ю-В Азия)", "Никель (London Metals Exchange)"], "target_value": 5900, "output_name": "Выручка"}</t>
+          <t>{"input_names": ["Коэффициент капитальных вложений", "Рост реального ВВП", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Хлорид калия (CFR Ю-В Азия)", "Никель (London Metals Exchange)"], "target_value": 5900, "output_name": "Выручка", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -18165,7 +18165,7 @@
       </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Средний за период курс рубля к доллару США (av USD/RUB)", "Ставка налога на прибыль организаций", "Медь (London Metals Exchange)", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)"], "target_value": 1.83, "output_name": "Net Debt/EBITDA"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Средний за период курс рубля к доллару США (av USD/RUB)", "Ставка налога на прибыль организаций", "Медь (London Metals Exchange)", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)"], "target_value": 1.83, "output_name": "Net Debt/EBITDA", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -18211,7 +18211,7 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Медь (London Metals Exchange)", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Цена урана", "Этилен, CFR Китай"], "target_value": 8.69, "output_name": "ICR corr (LTM)"}</t>
+          <t>{"input_names": ["Медь (London Metals Exchange)", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Цена урана", "Этилен, CFR Китай"], "target_value": 8.69, "output_name": "ICR corr (LTM)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -18257,7 +18257,7 @@
       </c>
       <c r="J13" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Медь (London Metals Exchange)", "Никель (London Metals Exchange)", "Метанол"], "target_value": 14.55, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)"}</t>
+          <t>{"input_names": ["Медь (London Metals Exchange)", "Никель (London Metals Exchange)", "Метанол"], "target_value": 14.55, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -18303,7 +18303,7 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент цены", "Hard Coking Coal (FOB Australia)", "Карбамид (FOB Южный)", "Ставка Euribor 3m"], "target_value": 9.36, "output_name": "ICR corr (LTM)"}</t>
+          <t>{"input_names": ["Коэффициент цены", "Hard Coking Coal (FOB Australia)", "Карбамид (FOB Южный)", "Ставка Euribor 3m"], "target_value": 9.36, "output_name": "ICR corr (LTM)", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -18349,7 +18349,7 @@
       </c>
       <c r="J15" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ставка Euribor 3m", "Коэффициент постоянных расходов", "Ставка Libor 3m", "Золото (London Metals Exchange)"], "target_value": 3950, "output_name": "Выручка"}</t>
+          <t>{"input_names": ["Ставка Euribor 3m", "Коэффициент постоянных расходов", "Ставка Libor 3m", "Золото (London Metals Exchange)"], "target_value": 3950, "output_name": "Выручка", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -18395,7 +18395,7 @@
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Цена на природный газ на хабе TTF", "Ставка Libor 3m", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Коэффициент объема", "Метанол"], "target_value": 700, "output_name": "Долг (Debt)"}</t>
+          <t>{"input_names": ["Цена на природный газ на хабе TTF", "Ставка Libor 3m", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Коэффициент объема", "Метанол"], "target_value": 700, "output_name": "Долг (Debt)", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -18441,7 +18441,7 @@
       </c>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ставка Libor 3m", "Коэффициент объема", "Алюминий (London Metals Exchange, без премии)"], "target_value": 600, "output_name": "Чистая прибыль"}</t>
+          <t>{"input_names": ["Ставка Libor 3m", "Коэффициент объема", "Алюминий (London Metals Exchange, без премии)"], "target_value": 600, "output_name": "Чистая прибыль", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -18487,7 +18487,7 @@
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Никель (London Metals Exchange)", "Цена урана", "Коэффициент цены"], "target_value": 6.79, "output_name": "Коэффициент покрытия процентов в i-ом периоде (ICR)"}</t>
+          <t>{"input_names": ["Никель (London Metals Exchange)", "Цена урана", "Коэффициент цены"], "target_value": 6.79, "output_name": "Коэффициент покрытия процентов в i-ом периоде (ICR)", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -18533,7 +18533,7 @@
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент постоянных расходов", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Ключевая ставка на конец года (eop)", "Цена урана", "Алюминий (London Metals Exchange, без премии)"], "target_value": 8.65, "output_name": "ICR corr (LTM)"}</t>
+          <t>{"input_names": ["Коэффициент постоянных расходов", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Ключевая ставка на конец года (eop)", "Цена урана", "Алюминий (London Metals Exchange, без премии)"], "target_value": 8.65, "output_name": "ICR corr (LTM)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Алюминий (London Metals Exchange, без премии)", "Коэффициент объема", "Метанол"], "target_value": 9.82, "output_name": "ICR (LTM)"}</t>
+          <t>{"input_names": ["Алюминий (London Metals Exchange, без премии)", "Коэффициент объема", "Метанол"], "target_value": 9.82, "output_name": "ICR (LTM)", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -18625,7 +18625,7 @@
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ставка Libor 3m", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Нефть марки Urals", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)"], "target_value": 470, "output_name": "Чистый денежный поток за период (NCF)"}</t>
+          <t>{"input_names": ["Ставка Libor 3m", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Нефть марки Urals", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)"], "target_value": 470, "output_name": "Чистый денежный поток за период (NCF)", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -18671,7 +18671,7 @@
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Hard Coking Coal (FOB Australia)", "Железная руда (Iron Ore 62%, CFR China)", "Ставка Euribor 3m"], "target_value": 8.76, "output_name": "ICR corr (LTM)"}</t>
+          <t>{"input_names": ["Hard Coking Coal (FOB Australia)", "Железная руда (Iron Ore 62%, CFR China)", "Ставка Euribor 3m"], "target_value": 8.76, "output_name": "ICR corr (LTM)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -18717,7 +18717,7 @@
       </c>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ставка Euribor 3m", "ECB policy rate (Main Refinancing Operations rate)", "Этилен, CFR Китай", "Метанол"], "target_value": 850, "output_name": "Денежные средства, доступные для обслуживания долга (CFADS)"}</t>
+          <t>{"input_names": ["Ставка Euribor 3m", "ECB policy rate (Main Refinancing Operations rate)", "Этилен, CFR Китай", "Метанол"], "target_value": 850, "output_name": "Денежные средства, доступные для обслуживания долга (CFADS)", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -18763,7 +18763,7 @@
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Никель (London Metals Exchange)", "Золото (London Metals Exchange)", "Hard Coking Coal (FOB Australia)"], "target_value": 3.61, "output_name": "Минимальный годичный DSCR"}</t>
+          <t>{"input_names": ["Никель (London Metals Exchange)", "Золото (London Metals Exchange)", "Hard Coking Coal (FOB Australia)"], "target_value": 3.61, "output_name": "Минимальный годичный DSCR", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Железная руда (Iron Ore 62%, CFR China)", "Хлорид калия (CFR Ю-В Азия)", "Никель (London Metals Exchange)"], "target_value": 10.88, "output_name": "Коэффициент покрытия процентов в i-ом периоде (ISCR)"}</t>
+          <t>{"input_names": ["Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Железная руда (Iron Ore 62%, CFR China)", "Хлорид калия (CFR Ю-В Азия)", "Никель (London Metals Exchange)"], "target_value": 10.88, "output_name": "Коэффициент покрытия процентов в i-ом периоде (ISCR)", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -18855,7 +18855,7 @@
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Этилен, CFR Китай", "Средний за период курс рубля к доллару США (av USD/RUB)", "Нефть марки Brent", "Коэффициент цены"], "target_value": 100, "output_name": "Платежи процентов по долговым обязательствам "}</t>
+          <t>{"input_names": ["Этилен, CFR Китай", "Средний за период курс рубля к доллару США (av USD/RUB)", "Нефть марки Brent", "Коэффициент цены"], "target_value": 100, "output_name": "Платежи процентов по долговым обязательствам ", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -18901,7 +18901,7 @@
       </c>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Медь (London Metals Exchange)", "Hard Coking Coal (FOB Australia)", "Рост реального ВВП"], "target_value": 5200, "output_name": "Выручка (LTM)"}</t>
+          <t>{"input_names": ["Медь (London Metals Exchange)", "Hard Coking Coal (FOB Australia)", "Рост реального ВВП"], "target_value": 5200, "output_name": "Выручка (LTM)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -18947,7 +18947,7 @@
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ставка Euribor 3m", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Медь (London Metals Exchange)", "Ставка налога на прибыль организаций"], "target_value": 6.05, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)"}</t>
+          <t>{"input_names": ["Ставка Euribor 3m", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Медь (London Metals Exchange)", "Ставка налога на прибыль организаций"], "target_value": 6.05, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -18993,7 +18993,7 @@
       </c>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент постоянных расходов", "Нефть марки Brent", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Алюминий (London Metals Exchange, без премии)"], "target_value": 15.25, "output_name": "ISCR (LTM)"}</t>
+          <t>{"input_names": ["Коэффициент постоянных расходов", "Нефть марки Brent", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Алюминий (London Metals Exchange, без премии)"], "target_value": 15.25, "output_name": "ISCR (LTM)", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -19039,7 +19039,7 @@
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Медь (London Metals Exchange)", "Рост реального ВВП", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": 22.14, "output_name": "Коэффициент покрытия процентов в i-ом периоде (ICR)"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Медь (London Metals Exchange)", "Рост реального ВВП", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": 22.14, "output_name": "Коэффициент покрытия процентов в i-ом периоде (ICR)", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -19085,7 +19085,7 @@
       </c>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Коэффициент объема", "Курс рубля к доллару США в конце года (eop USD/RUB)"], "target_value": -1000, "output_name": "Чистый долг (Net Debt)"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Коэффициент объема", "Курс рубля к доллару США в конце года (eop USD/RUB)"], "target_value": -1000, "output_name": "Чистый долг (Net Debt)", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -19131,7 +19131,7 @@
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Этилен, CFR Китай", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Цена урана", "Ставка Euribor 3m"], "target_value": 90, "output_name": "Платежи процентов по долговым обязательствам "}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Этилен, CFR Китай", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Цена урана", "Ставка Euribor 3m"], "target_value": 90, "output_name": "Платежи процентов по долговым обязательствам ", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -19177,7 +19177,7 @@
       </c>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Цена на природный газ на хабе Henry Hub", "Ставка Libor 3m", "Никель (London Metals Exchange)", "Курс рубля к доллару США в конце года (eop USD/RUB)"], "target_value": 2000, "output_name": "Долг (Debt)"}</t>
+          <t>{"input_names": ["Цена на природный газ на хабе Henry Hub", "Ставка Libor 3m", "Никель (London Metals Exchange)", "Курс рубля к доллару США в конце года (eop USD/RUB)"], "target_value": 2000, "output_name": "Долг (Debt)", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -19223,7 +19223,7 @@
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Хлорид калия (CFR Ю-В Азия)", "Цена на природный газ на хабе TTF", "ECB policy rate (Main Refinancing Operations rate)"], "target_value": 1100, "output_name": "EBITDA"}</t>
+          <t>{"input_names": ["Хлорид калия (CFR Ю-В Азия)", "Цена на природный газ на хабе TTF", "ECB policy rate (Main Refinancing Operations rate)"], "target_value": 1100, "output_name": "EBITDA", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -19269,7 +19269,7 @@
       </c>
       <c r="J35" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Нефть марки Brent", "Этилен, CFR Китай", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Аммиак (FOB Черное море)"], "target_value": 14.11, "output_name": "ICR corr"}</t>
+          <t>{"input_names": ["Нефть марки Brent", "Этилен, CFR Китай", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Аммиак (FOB Черное море)"], "target_value": 14.11, "output_name": "ICR corr", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -19315,7 +19315,7 @@
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Карбамид (FOB Южный)", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Алюминий (London Metals Exchange, без премии)"], "target_value": 2.46, "output_name": "Net Debt/EBITDA"}</t>
+          <t>{"input_names": ["Карбамид (FOB Южный)", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Алюминий (London Metals Exchange, без премии)"], "target_value": 2.46, "output_name": "Net Debt/EBITDA", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -19361,7 +19361,7 @@
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Средний за период курс рубля к доллару США (av USD/RUB)", "Коэффициент цены", "Коэффициент объема", "Цена на природный газ на хабе Henry Hub", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)"], "target_value": 8.0, "output_name": "ICR (LTM)"}</t>
+          <t>{"input_names": ["Средний за период курс рубля к доллару США (av USD/RUB)", "Коэффициент цены", "Коэффициент объема", "Цена на природный газ на хабе Henry Hub", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)"], "target_value": 8.0, "output_name": "ICR (LTM)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -19407,7 +19407,7 @@
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Аммиак (FOB Черное море)", "Карбамид (FOB Южный)", "Никель (London Metals Exchange)"], "target_value": 0.187, "output_name": "Рентабельность EBITDA (LTM)"}</t>
+          <t>{"input_names": ["Аммиак (FOB Черное море)", "Карбамид (FOB Южный)", "Никель (London Metals Exchange)"], "target_value": 0.187, "output_name": "Рентабельность EBITDA (LTM)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -19453,7 +19453,7 @@
       </c>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент цены", "Этилен, CFR Китай", "ECB policy rate (Main Refinancing Operations rate)"], "target_value": 0.28, "output_name": "Рентабельность EBITDA (LTM)"}</t>
+          <t>{"input_names": ["Коэффициент цены", "Этилен, CFR Китай", "ECB policy rate (Main Refinancing Operations rate)"], "target_value": 0.28, "output_name": "Рентабельность EBITDA (LTM)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -19499,7 +19499,7 @@
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Рост реального ВВП", "Карбамид (FOB Южный)", "Коэффициент удельных расходов", "Бензол, CFR Япония"], "target_value": 4300, "output_name": "Выручка"}</t>
+          <t>{"input_names": ["Рост реального ВВП", "Карбамид (FOB Южный)", "Коэффициент удельных расходов", "Бензол, CFR Япония"], "target_value": 4300, "output_name": "Выручка", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -19545,7 +19545,7 @@
       </c>
       <c r="J41" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Hard Coking Coal (FOB Australia)", "Цена на природный газ на хабе Henry Hub", "Ставка налога на прибыль организаций", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)"], "target_value": -290, "output_name": "Денежные потоки от финансовых операций (CFF)"}</t>
+          <t>{"input_names": ["Hard Coking Coal (FOB Australia)", "Цена на природный газ на хабе Henry Hub", "Ставка налога на прибыль организаций", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)"], "target_value": -290, "output_name": "Денежные потоки от финансовых операций (CFF)", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -19591,7 +19591,7 @@
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент удельных расходов", "Карбамид (FOB Южный)", "Ставка Libor 3m", "Бензол, CFR Япония", "Ставка Euribor 3m"], "target_value": 8.3, "output_name": "Коэффициент покрытия процентов в i-ом периоде (ISCR)"}</t>
+          <t>{"input_names": ["Коэффициент удельных расходов", "Карбамид (FOB Южный)", "Ставка Libor 3m", "Бензол, CFR Япония", "Ставка Euribor 3m"], "target_value": 8.3, "output_name": "Коэффициент покрытия процентов в i-ом периоде (ISCR)", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -19637,7 +19637,7 @@
       </c>
       <c r="J43" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Нефть марки Brent", "Коэффициент удельных расходов", "Карбамид (FOB Южный)", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Хлорид калия (CFR Ю-В Азия)"], "target_value": 4550, "output_name": "Выручка (LTM)"}</t>
+          <t>{"input_names": ["Нефть марки Brent", "Коэффициент удельных расходов", "Карбамид (FOB Южный)", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Хлорид калия (CFR Ю-В Азия)"], "target_value": 4550, "output_name": "Выручка (LTM)", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -19683,7 +19683,7 @@
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Ставка Euribor 3m", "Нефть марки Brent", "Цена урана", "Аммиак (FOB Черное море)"], "target_value": 800, "output_name": "EBITDA"}</t>
+          <t>{"input_names": ["Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Ставка Euribor 3m", "Нефть марки Brent", "Цена урана", "Аммиак (FOB Черное море)"], "target_value": 800, "output_name": "EBITDA", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -19729,7 +19729,7 @@
       </c>
       <c r="J45" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Бензол, CFR Япония", "Карбамид (FOB Южный)", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": 1000, "output_name": "Свободный денежный поток (FCFF)"}</t>
+          <t>{"input_names": ["Бензол, CFR Япония", "Карбамид (FOB Южный)", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": 1000, "output_name": "Свободный денежный поток (FCFF)", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -19775,7 +19775,7 @@
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Никель (London Metals Exchange)", "Коэффициент удельных расходов", "Ставка налога на прибыль организаций", "Нефть марки Brent"], "target_value": 10.56, "output_name": "ICR (LTM)"}</t>
+          <t>{"input_names": ["Никель (London Metals Exchange)", "Коэффициент удельных расходов", "Ставка налога на прибыль организаций", "Нефть марки Brent"], "target_value": 10.56, "output_name": "ICR (LTM)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Этилен, CFR Китай", "Алюминий (London Metals Exchange, без премии)", "Аммиак (FOB Черное море)"], "target_value": 5.46, "output_name": "DSCR (LTM)"}</t>
+          <t>{"input_names": ["Этилен, CFR Китай", "Алюминий (London Metals Exchange, без премии)", "Аммиак (FOB Черное море)"], "target_value": 5.46, "output_name": "DSCR (LTM)", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -19867,7 +19867,7 @@
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Коэффициент объема", "Медь (London Metals Exchange)"], "target_value": 360, "output_name": "Амортизация"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Коэффициент объема", "Медь (London Metals Exchange)"], "target_value": 360, "output_name": "Амортизация", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -19913,7 +19913,7 @@
       </c>
       <c r="J49" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["ECB policy rate (Main Refinancing Operations rate)", "Цена на природный газ на хабе Henry Hub", "Цена на природный газ на хабе TTF"], "target_value": 4.51, "output_name": "ICR corr (LTM)"}</t>
+          <t>{"input_names": ["ECB policy rate (Main Refinancing Operations rate)", "Цена на природный газ на хабе Henry Hub", "Цена на природный газ на хабе TTF"], "target_value": 4.51, "output_name": "ICR corr (LTM)", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -19959,7 +19959,7 @@
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Коэффициент удельных расходов", "Медь (London Metals Exchange)"], "target_value": 12.22, "output_name": "ISCR (LTM)"}</t>
+          <t>{"input_names": ["Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Коэффициент удельных расходов", "Медь (London Metals Exchange)"], "target_value": 12.22, "output_name": "ISCR (LTM)", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -20005,7 +20005,7 @@
       </c>
       <c r="J51" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Нефть марки Urals", "Никель (London Metals Exchange)", "Ставка налога на прибыль организаций", "Карбамид (FOB Южный)"], "target_value": 5100, "output_name": "Выручка"}</t>
+          <t>{"input_names": ["Нефть марки Urals", "Никель (London Metals Exchange)", "Ставка налога на прибыль организаций", "Карбамид (FOB Южный)"], "target_value": 5100, "output_name": "Выручка", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -20051,7 +20051,7 @@
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Аммиак (FOB Черное море)", "Медь (London Metals Exchange)", "Коэффициент постоянных расходов", "Коэффициент объема"], "target_value": 360, "output_name": "Чистая прибыль"}</t>
+          <t>{"input_names": ["Аммиак (FOB Черное море)", "Медь (London Metals Exchange)", "Коэффициент постоянных расходов", "Коэффициент объема"], "target_value": 360, "output_name": "Чистая прибыль", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -20097,7 +20097,7 @@
       </c>
       <c r="J53" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент объема", "Железная руда (Iron Ore 62%, CFR China)", "Цена на природный газ на хабе TTF"], "target_value": 8.17, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)"}</t>
+          <t>{"input_names": ["Коэффициент объема", "Железная руда (Iron Ore 62%, CFR China)", "Цена на природный газ на хабе TTF"], "target_value": 8.17, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -20143,7 +20143,7 @@
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ключевая ставка на конец года (eop)", "Железная руда (Iron Ore 62%, CFR China)", "Метанол", "Хлорид калия (CFR Ю-В Азия)", "ECB policy rate (Main Refinancing Operations rate)"], "target_value": 3650, "output_name": "Выручка"}</t>
+          <t>{"input_names": ["Ключевая ставка на конец года (eop)", "Железная руда (Iron Ore 62%, CFR China)", "Метанол", "Хлорид калия (CFR Ю-В Азия)", "ECB policy rate (Main Refinancing Operations rate)"], "target_value": 3650, "output_name": "Выручка", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -20189,7 +20189,7 @@
       </c>
       <c r="J55" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Средний за период курс рубля к доллару США (av USD/RUB)", "ECB policy rate (Main Refinancing Operations rate)", "Никель (London Metals Exchange)"], "target_value": 0.105, "output_name": "Рентабельность чистой прибыли"}</t>
+          <t>{"input_names": ["Средний за период курс рубля к доллару США (av USD/RUB)", "ECB policy rate (Main Refinancing Operations rate)", "Никель (London Metals Exchange)"], "target_value": 0.105, "output_name": "Рентабельность чистой прибыли", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -20235,7 +20235,7 @@
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Курс рубля к EUR в конце года (eop EUR/RUB)", "ECB policy rate (Main Refinancing Operations rate)", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)"], "target_value": 6.51, "output_name": "ICR corr (LTM)"}</t>
+          <t>{"input_names": ["Курс рубля к EUR в конце года (eop EUR/RUB)", "ECB policy rate (Main Refinancing Operations rate)", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)"], "target_value": 6.51, "output_name": "ICR corr (LTM)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -20281,7 +20281,7 @@
       </c>
       <c r="J57" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Курс рубля к EUR в конце года (eop EUR/RUB)", "Нефть марки Brent", "Цена урана"], "target_value": 2.8, "output_name": "Net Debt/EBITDA"}</t>
+          <t>{"input_names": ["Курс рубля к EUR в конце года (eop EUR/RUB)", "Нефть марки Brent", "Цена урана"], "target_value": 2.8, "output_name": "Net Debt/EBITDA", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -20327,7 +20327,7 @@
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Средний за период курс рубля к доллару США (av USD/RUB)", "Аммиак (FOB Черное море)", "Карбамид (FOB Южный)", "Цена урана", "Курс рубля к EUR в конце года (eop EUR/RUB)"], "target_value": 750, "output_name": "Денежные потоки от текущих операций (CFO)"}</t>
+          <t>{"input_names": ["Средний за период курс рубля к доллару США (av USD/RUB)", "Аммиак (FOB Черное море)", "Карбамид (FOB Южный)", "Цена урана", "Курс рубля к EUR в конце года (eop EUR/RUB)"], "target_value": 750, "output_name": "Денежные потоки от текущих операций (CFO)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -20373,7 +20373,7 @@
       </c>
       <c r="J59" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Коэффициент цены", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Курс рубля к EUR в конце года (eop EUR/RUB)"], "target_value": 490, "output_name": "Чистая прибыль"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Коэффициент цены", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Курс рубля к EUR в конце года (eop EUR/RUB)"], "target_value": 490, "output_name": "Чистая прибыль", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -20419,7 +20419,7 @@
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Этилен, CFR Китай", "Цена урана", "Золото (London Metals Exchange)"], "target_value": 6.03, "output_name": "DSCR (LTM)"}</t>
+          <t>{"input_names": ["Этилен, CFR Китай", "Цена урана", "Золото (London Metals Exchange)"], "target_value": 6.03, "output_name": "DSCR (LTM)", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -20465,7 +20465,7 @@
       </c>
       <c r="J61" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Метанол", "Золото (London Metals Exchange)", "Бензол, CFR Япония"], "target_value": 0.122, "output_name": "Рентабельность чистой прибыли"}</t>
+          <t>{"input_names": ["Метанол", "Золото (London Metals Exchange)", "Бензол, CFR Япония"], "target_value": 0.122, "output_name": "Рентабельность чистой прибыли", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -20511,7 +20511,7 @@
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Курс рубля к EUR в конце года (eop EUR/RUB)", "Цена урана", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)"], "target_value": 1.94, "output_name": "Net Debt/EBITDA (LTM)"}</t>
+          <t>{"input_names": ["Курс рубля к EUR в конце года (eop EUR/RUB)", "Цена урана", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)"], "target_value": 1.94, "output_name": "Net Debt/EBITDA (LTM)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -20557,7 +20557,7 @@
       </c>
       <c r="J63" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "ECB policy rate (Main Refinancing Operations rate)", "Цена урана", "Золото (London Metals Exchange)"], "target_value": 120, "output_name": "Обслуживание долга (Debt Service)"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "ECB policy rate (Main Refinancing Operations rate)", "Цена урана", "Золото (London Metals Exchange)"], "target_value": 120, "output_name": "Обслуживание долга (Debt Service)", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -20603,7 +20603,7 @@
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Цена урана", "Карбамид (FOB Южный)", "Нефть марки Urals", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": 410, "output_name": "Амортизация"}</t>
+          <t>{"input_names": ["Цена урана", "Карбамид (FOB Южный)", "Нефть марки Urals", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": 410, "output_name": "Амортизация", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -20649,7 +20649,7 @@
       </c>
       <c r="J65" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Хлорид калия (CFR Ю-В Азия)", "Ставка Libor 3m", "Коэффициент удельных расходов", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": 650, "output_name": "Свободный денежный поток (FCFF)"}</t>
+          <t>{"input_names": ["Хлорид калия (CFR Ю-В Азия)", "Ставка Libor 3m", "Коэффициент удельных расходов", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": 650, "output_name": "Свободный денежный поток (FCFF)", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -20695,7 +20695,7 @@
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Рост реального ВВП", "Коэффициент капитальных вложений"], "target_value": -280, "output_name": "Чистый денежный поток за период (NCF)"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Рост реального ВВП", "Коэффициент капитальных вложений"], "target_value": -280, "output_name": "Чистый денежный поток за период (NCF)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -20741,7 +20741,7 @@
       </c>
       <c r="J67" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Курс рубля к EUR в конце года (eop EUR/RUB)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Коэффициент удельных расходов"], "target_value": -1250, "output_name": "Чистый долг (Net Debt)"}</t>
+          <t>{"input_names": ["Курс рубля к EUR в конце года (eop EUR/RUB)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Коэффициент удельных расходов"], "target_value": -1250, "output_name": "Чистый долг (Net Debt)", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -20787,7 +20787,7 @@
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Этилен, CFR Китай", "Коэффициент цены", "Hard Coking Coal (FOB Australia)", "Курс рубля к доллару США в конце года (eop USD/RUB)"], "target_value": 1.31, "output_name": "Net Debt/EBITDA (LTM)"}</t>
+          <t>{"input_names": ["Этилен, CFR Китай", "Коэффициент цены", "Hard Coking Coal (FOB Australia)", "Курс рубля к доллару США в конце года (eop USD/RUB)"], "target_value": 1.31, "output_name": "Net Debt/EBITDA (LTM)", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -20833,7 +20833,7 @@
       </c>
       <c r="J69" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Цена на природный газ на хабе Henry Hub", "Карбамид (FOB Южный)", "Коэффициент капитальных вложений", "Нефть марки Brent", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": 240, "output_name": "Амортизация"}</t>
+          <t>{"input_names": ["Цена на природный газ на хабе Henry Hub", "Карбамид (FOB Южный)", "Коэффициент капитальных вложений", "Нефть марки Brent", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": 240, "output_name": "Амортизация", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -20879,7 +20879,7 @@
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Средний за период курс рубля к доллару США (av USD/RUB)", "Нефть марки Brent", "Метанол", "Медь (London Metals Exchange)", "Ставка налога на прибыль организаций"], "target_value": 400, "output_name": "Амортизация"}</t>
+          <t>{"input_names": ["Средний за период курс рубля к доллару США (av USD/RUB)", "Нефть марки Brent", "Метанол", "Медь (London Metals Exchange)", "Ставка налога на прибыль организаций"], "target_value": 400, "output_name": "Амортизация", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -20925,7 +20925,7 @@
       </c>
       <c r="J71" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Алюминий (London Metals Exchange, без премии)", "Коэффициент постоянных расходов", "Средний за период курс рубля к доллару США (av USD/RUB)", "Железная руда (Iron Ore 62%, CFR China)"], "target_value": 650, "output_name": "Свободный денежный поток (FCFF)"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Алюминий (London Metals Exchange, без премии)", "Коэффициент постоянных расходов", "Средний за период курс рубля к доллару США (av USD/RUB)", "Железная руда (Iron Ore 62%, CFR China)"], "target_value": 650, "output_name": "Свободный денежный поток (FCFF)", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -20971,7 +20971,7 @@
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Метанол", "Курс рубля к доллару США в конце года (eop USD/RUB)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)"], "target_value": 180, "output_name": "Сумма капитальных затрат (CAPEX)"}</t>
+          <t>{"input_names": ["Метанол", "Курс рубля к доллару США в конце года (eop USD/RUB)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)"], "target_value": 180, "output_name": "Сумма капитальных затрат (CAPEX)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -21017,7 +21017,7 @@
       </c>
       <c r="J73" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Цена на природный газ на хабе TTF", "Коэффициент капитальных вложений", "Железная руда (Iron Ore 62%, CFR China)"], "target_value": 110, "output_name": "Обслуживание долга (Debt Service)"}</t>
+          <t>{"input_names": ["Цена на природный газ на хабе TTF", "Коэффициент капитальных вложений", "Железная руда (Iron Ore 62%, CFR China)"], "target_value": 110, "output_name": "Обслуживание долга (Debt Service)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -21063,7 +21063,7 @@
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Аммиак (FOB Черное море)", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Цена на природный газ на хабе Henry Hub"], "target_value": 3450, "output_name": "Выручка (LTM)"}</t>
+          <t>{"input_names": ["Аммиак (FOB Черное море)", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Цена на природный газ на хабе Henry Hub"], "target_value": 3450, "output_name": "Выручка (LTM)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -21109,7 +21109,7 @@
       </c>
       <c r="J75" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Курс рубля к EUR в конце года (eop EUR/RUB)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Метанол", "Цена на природный газ на хабе Henry Hub"], "target_value": 0.74, "output_name": "Debt/EBITDA"}</t>
+          <t>{"input_names": ["Курс рубля к EUR в конце года (eop EUR/RUB)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Метанол", "Цена на природный газ на хабе Henry Hub"], "target_value": 0.74, "output_name": "Debt/EBITDA", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -21155,7 +21155,7 @@
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Рост реального ВВП", "Аммиак (FOB Черное море)", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)"], "target_value": 3650, "output_name": "Выручка (LTM)"}</t>
+          <t>{"input_names": ["Рост реального ВВП", "Аммиак (FOB Черное море)", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)"], "target_value": 3650, "output_name": "Выручка (LTM)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -21201,7 +21201,7 @@
       </c>
       <c r="J77" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент объема", "Цена урана", "Ставка налога на прибыль организаций", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Этилен, CFR Китай"], "target_value": -800, "output_name": "Денежные потоки от финансовых операций (CFF)"}</t>
+          <t>{"input_names": ["Коэффициент объема", "Цена урана", "Ставка налога на прибыль организаций", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Этилен, CFR Китай"], "target_value": -800, "output_name": "Денежные потоки от финансовых операций (CFF)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -21247,7 +21247,7 @@
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Курс рубля к доллару США в конце года (eop USD/RUB)", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Аммиак (FOB Черное море)"], "target_value": 2.6, "output_name": "Net Debt/EBITDA"}</t>
+          <t>{"input_names": ["Курс рубля к доллару США в конце года (eop USD/RUB)", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Аммиак (FOB Черное море)"], "target_value": 2.6, "output_name": "Net Debt/EBITDA", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -21293,7 +21293,7 @@
       </c>
       <c r="J79" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Средний за период курс рубля к доллару США (av USD/RUB)", "Ключевая ставка на конец года (eop)", "Ставка налога на прибыль организаций"], "target_value": 1000, "output_name": "EBITDA"}</t>
+          <t>{"input_names": ["Средний за период курс рубля к доллару США (av USD/RUB)", "Ключевая ставка на конец года (eop)", "Ставка налога на прибыль организаций"], "target_value": 1000, "output_name": "EBITDA", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -21339,7 +21339,7 @@
       </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Курс рубля к EUR в конце года (eop EUR/RUB)", "Коэффициент объема", "Железная руда (Iron Ore 62%, CFR China)", "Коэффициент капитальных вложений"], "target_value": 7.37, "output_name": "ISCR (LTM)"}</t>
+          <t>{"input_names": ["Курс рубля к EUR в конце года (eop EUR/RUB)", "Коэффициент объема", "Железная руда (Iron Ore 62%, CFR China)", "Коэффициент капитальных вложений"], "target_value": 7.37, "output_name": "ISCR (LTM)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -21385,7 +21385,7 @@
       </c>
       <c r="J81" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент капитальных вложений", "Аммиак (FOB Черное море)", "Медь (London Metals Exchange)", "Никель (London Metals Exchange)"], "target_value": 0.108, "output_name": "Рентабельность чистой прибыли"}</t>
+          <t>{"input_names": ["Коэффициент капитальных вложений", "Аммиак (FOB Черное море)", "Медь (London Metals Exchange)", "Никель (London Metals Exchange)"], "target_value": 0.108, "output_name": "Рентабельность чистой прибыли", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -21431,7 +21431,7 @@
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент цены", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Коэффициент капитальных вложений", "ECB policy rate (Main Refinancing Operations rate)", "Цена урана"], "target_value": 7.15, "output_name": "ICR corr"}</t>
+          <t>{"input_names": ["Коэффициент цены", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Коэффициент капитальных вложений", "ECB policy rate (Main Refinancing Operations rate)", "Цена урана"], "target_value": 7.15, "output_name": "ICR corr", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -21477,7 +21477,7 @@
       </c>
       <c r="J83" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Нефть марки Brent", "Цена на природный газ на хабе Henry Hub", "Цена на природный газ на хабе TTF", "Золото (London Metals Exchange)"], "target_value": 800, "output_name": "Остаток денежных средств на конец периода"}</t>
+          <t>{"input_names": ["Нефть марки Brent", "Цена на природный газ на хабе Henry Hub", "Цена на природный газ на хабе TTF", "Золото (London Metals Exchange)"], "target_value": 800, "output_name": "Остаток денежных средств на конец периода", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -21523,7 +21523,7 @@
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Курс рубля к EUR в конце года (eop EUR/RUB)", "Коэффициент объема", "Никель (London Metals Exchange)"], "target_value": 800, "output_name": "EBITDA (LTM)"}</t>
+          <t>{"input_names": ["Курс рубля к EUR в конце года (eop EUR/RUB)", "Коэффициент объема", "Никель (London Metals Exchange)"], "target_value": 800, "output_name": "EBITDA (LTM)", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -21569,7 +21569,7 @@
       </c>
       <c r="J85" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Никель (London Metals Exchange)", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Hard Coking Coal (FOB Australia)"], "target_value": 6.91, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)"}</t>
+          <t>{"input_names": ["Никель (London Metals Exchange)", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Hard Coking Coal (FOB Australia)"], "target_value": 6.91, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -21615,7 +21615,7 @@
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент удельных расходов", "Аммиак (FOB Черное море)", "Ставка налога на прибыль организаций", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Никель (London Metals Exchange)"], "target_value": 280, "output_name": "Амортизация"}</t>
+          <t>{"input_names": ["Коэффициент удельных расходов", "Аммиак (FOB Черное море)", "Ставка налога на прибыль организаций", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Никель (London Metals Exchange)"], "target_value": 280, "output_name": "Амортизация", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -21661,7 +21661,7 @@
       </c>
       <c r="J87" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Нефть марки Brent", "Средний за период курс рубля к доллару США (av USD/RUB)", "Бензол, CFR Япония"], "target_value": 70, "output_name": "Платежи процентов по долговым обязательствам "}</t>
+          <t>{"input_names": ["Нефть марки Brent", "Средний за период курс рубля к доллару США (av USD/RUB)", "Бензол, CFR Япония"], "target_value": 70, "output_name": "Платежи процентов по долговым обязательствам ", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -21707,7 +21707,7 @@
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Средний за период курс рубля к доллару США (av USD/RUB)", "Ставка Libor 3m", "Ключевая ставка на конец года (eop)", "Золото (London Metals Exchange)", "Нефть марки Urals"], "target_value": 3150, "output_name": "Долг (Debt)"}</t>
+          <t>{"input_names": ["Средний за период курс рубля к доллару США (av USD/RUB)", "Ставка Libor 3m", "Ключевая ставка на конец года (eop)", "Золото (London Metals Exchange)", "Нефть марки Urals"], "target_value": 3150, "output_name": "Долг (Debt)", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -21753,7 +21753,7 @@
       </c>
       <c r="J89" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Золото (London Metals Exchange)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Алюминий (London Metals Exchange, без премии)"], "target_value": 0.201, "output_name": "Рентабельность EBITDA (LTM)"}</t>
+          <t>{"input_names": ["Золото (London Metals Exchange)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Алюминий (London Metals Exchange, без премии)"], "target_value": 0.201, "output_name": "Рентабельность EBITDA (LTM)", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -21799,7 +21799,7 @@
       </c>
       <c r="J90" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ставка Libor 3m", "Цена на природный газ на хабе TTF", "Карбамид (FOB Южный)"], "target_value": 900, "output_name": "Денежные средства, доступные для обслуживания долга (CFADS)"}</t>
+          <t>{"input_names": ["Ставка Libor 3m", "Цена на природный газ на хабе TTF", "Карбамид (FOB Южный)"], "target_value": 900, "output_name": "Денежные средства, доступные для обслуживания долга (CFADS)", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -21845,7 +21845,7 @@
       </c>
       <c r="J91" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент объема", "Медь (London Metals Exchange)", "Hard Coking Coal (FOB Australia)", "Ставка Euribor 3m"], "target_value": 950, "output_name": "Свободный денежный поток (FCFF)"}</t>
+          <t>{"input_names": ["Коэффициент объема", "Медь (London Metals Exchange)", "Hard Coking Coal (FOB Australia)", "Ставка Euribor 3m"], "target_value": 950, "output_name": "Свободный денежный поток (FCFF)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -21891,7 +21891,7 @@
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Нефть марки Brent", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Нефть марки Urals", "Алюминий (London Metals Exchange, без премии)"], "target_value": -280, "output_name": "Денежные потоки от финансовых операций (CFF)"}</t>
+          <t>{"input_names": ["Нефть марки Brent", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Нефть марки Urals", "Алюминий (London Metals Exchange, без премии)"], "target_value": -280, "output_name": "Денежные потоки от финансовых операций (CFF)", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -21937,7 +21937,7 @@
       </c>
       <c r="J93" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Ставка Euribor 3m", "Никель (London Metals Exchange)", "Курс рубля к EUR в конце года (eop EUR/RUB)"], "target_value": 4550, "output_name": "Выручка"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Ставка Euribor 3m", "Никель (London Metals Exchange)", "Курс рубля к EUR в конце года (eop EUR/RUB)"], "target_value": 4550, "output_name": "Выручка", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -21983,7 +21983,7 @@
       </c>
       <c r="J94" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Никель (London Metals Exchange)", "Ключевая ставка на конец года (eop)", "Цена урана", "Коэффициент постоянных расходов"], "target_value": 110, "output_name": "Платежи процентов по долговым обязательствам "}</t>
+          <t>{"input_names": ["Никель (London Metals Exchange)", "Ключевая ставка на конец года (eop)", "Цена урана", "Коэффициент постоянных расходов"], "target_value": 110, "output_name": "Платежи процентов по долговым обязательствам ", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="J95" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ключевая ставка на конец года (eop)", "Цена урана", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)"], "target_value": 200, "output_name": "Сумма капитальных затрат (CAPEX)"}</t>
+          <t>{"input_names": ["Ключевая ставка на конец года (eop)", "Цена урана", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)"], "target_value": 200, "output_name": "Сумма капитальных затрат (CAPEX)", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -22075,7 +22075,7 @@
       </c>
       <c r="J96" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент постоянных расходов", "Ключевая ставка на конец года (eop)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)"], "target_value": 1100, "output_name": "Денежные потоки от текущих операций (CFO)"}</t>
+          <t>{"input_names": ["Коэффициент постоянных расходов", "Ключевая ставка на конец года (eop)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)"], "target_value": 1100, "output_name": "Денежные потоки от текущих операций (CFO)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -22121,7 +22121,7 @@
       </c>
       <c r="J97" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Коэффициент цены", "Этилен, CFR Китай", "Рост реального ВВП"], "target_value": 100, "output_name": "Обслуживание долга (Debt Service)"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Коэффициент цены", "Этилен, CFR Китай", "Рост реального ВВП"], "target_value": 100, "output_name": "Обслуживание долга (Debt Service)", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -22167,7 +22167,7 @@
       </c>
       <c r="J98" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": 80, "output_name": "Обслуживание долга (Debt Service)"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": 80, "output_name": "Обслуживание долга (Debt Service)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -22213,7 +22213,7 @@
       </c>
       <c r="J99" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["ECB policy rate (Main Refinancing Operations rate)", "Золото (London Metals Exchange)", "Коэффициент удельных расходов"], "target_value": 3.51, "output_name": "Минимальный годичный DSCR"}</t>
+          <t>{"input_names": ["ECB policy rate (Main Refinancing Operations rate)", "Золото (London Metals Exchange)", "Коэффициент удельных расходов"], "target_value": 3.51, "output_name": "Минимальный годичный DSCR", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -22259,7 +22259,7 @@
       </c>
       <c r="J100" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Медь (London Metals Exchange)", "Ключевая ставка на конец года (eop)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Коэффициент постоянных расходов"], "target_value": 650, "output_name": "Долг (Debt)"}</t>
+          <t>{"input_names": ["Медь (London Metals Exchange)", "Ключевая ставка на конец года (eop)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Коэффициент постоянных расходов"], "target_value": 650, "output_name": "Долг (Debt)", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -22305,7 +22305,7 @@
       </c>
       <c r="J101" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Никель (London Metals Exchange)", "Ставка Euribor 3m", "Карбамид (FOB Южный)", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)"], "target_value": 850, "output_name": "Чистый долг (Net Debt)"}</t>
+          <t>{"input_names": ["Никель (London Metals Exchange)", "Ставка Euribor 3m", "Карбамид (FOB Южный)", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)"], "target_value": 850, "output_name": "Чистый долг (Net Debt)", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -22351,7 +22351,7 @@
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Нефть марки Brent", "Железная руда (Iron Ore 62%, CFR China)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Цена на природный газ на хабе Henry Hub", "Карбамид (FOB Южный)"], "target_value": 9.11, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)"}</t>
+          <t>{"input_names": ["Нефть марки Brent", "Железная руда (Iron Ore 62%, CFR China)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Цена на природный газ на хабе Henry Hub", "Карбамид (FOB Южный)"], "target_value": 9.11, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -22397,7 +22397,7 @@
       </c>
       <c r="J103" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Курс рубля к доллару США в конце года (eop USD/RUB)", "Карбамид (FOB Южный)", "Цена урана"], "target_value": 0.161, "output_name": "Рентабельность EBITDA (LTM)"}</t>
+          <t>{"input_names": ["Курс рубля к доллару США в конце года (eop USD/RUB)", "Карбамид (FOB Южный)", "Цена урана"], "target_value": 0.161, "output_name": "Рентабельность EBITDA (LTM)", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -22443,7 +22443,7 @@
       </c>
       <c r="J104" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Никель (London Metals Exchange)", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Цена на природный газ на хабе Henry Hub", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)"], "target_value": 0.117, "output_name": "Рентабельность чистой прибыли"}</t>
+          <t>{"input_names": ["Никель (London Metals Exchange)", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Цена на природный газ на хабе Henry Hub", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)"], "target_value": 0.117, "output_name": "Рентабельность чистой прибыли", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -22489,7 +22489,7 @@
       </c>
       <c r="J105" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Нефть марки Urals", "Медь (London Metals Exchange)", "Коэффициент цены", "Коэффициент капитальных вложений", "Цена на природный газ на хабе Henry Hub"], "target_value": 0.66, "output_name": "Net Debt/EBITDA"}</t>
+          <t>{"input_names": ["Нефть марки Urals", "Медь (London Metals Exchange)", "Коэффициент цены", "Коэффициент капитальных вложений", "Цена на природный газ на хабе Henry Hub"], "target_value": 0.66, "output_name": "Net Debt/EBITDA", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -22535,7 +22535,7 @@
       </c>
       <c r="J106" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Рост реального ВВП", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Аммиак (FOB Черное море)", "Метанол"], "target_value": 6.05, "output_name": "Коэффициент покрытия процентов в i-ом периоде (ICR)"}</t>
+          <t>{"input_names": ["Рост реального ВВП", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Аммиак (FOB Черное море)", "Метанол"], "target_value": 6.05, "output_name": "Коэффициент покрытия процентов в i-ом периоде (ICR)", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -22581,7 +22581,7 @@
       </c>
       <c r="J107" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Цена урана", "Золото (London Metals Exchange)", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)"], "target_value": 85, "output_name": "Проценты к уплате"}</t>
+          <t>{"input_names": ["Цена урана", "Золото (London Metals Exchange)", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)"], "target_value": 85, "output_name": "Проценты к уплате", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -22627,7 +22627,7 @@
       </c>
       <c r="J108" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Хлорид калия (CFR Ю-В Азия)", "Золото (London Metals Exchange)", "Коэффициент удельных расходов", "Курс рубля к EUR в конце года (eop EUR/RUB)"], "target_value": 500, "output_name": "Свободный денежный поток (FCFF)"}</t>
+          <t>{"input_names": ["Хлорид калия (CFR Ю-В Азия)", "Золото (London Metals Exchange)", "Коэффициент удельных расходов", "Курс рубля к EUR в конце года (eop EUR/RUB)"], "target_value": 500, "output_name": "Свободный денежный поток (FCFF)", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="J109" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Метанол", "Нефть марки Urals", "Алюминий (London Metals Exchange, без премии)", "Коэффициент удельных расходов"], "target_value": 5600, "output_name": "Выручка (LTM)"}</t>
+          <t>{"input_names": ["Метанол", "Нефть марки Urals", "Алюминий (London Metals Exchange, без премии)", "Коэффициент удельных расходов"], "target_value": 5600, "output_name": "Выручка (LTM)", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -22719,7 +22719,7 @@
       </c>
       <c r="J110" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Алюминий (London Metals Exchange, без премии)", "Этилен, CFR Китай", "Коэффициент цены", "Коэффициент капитальных вложений", "Рост реального ВВП"], "target_value": 120, "output_name": "Обслуживание долга (Debt Service)"}</t>
+          <t>{"input_names": ["Алюминий (London Metals Exchange, без премии)", "Этилен, CFR Китай", "Коэффициент цены", "Коэффициент капитальных вложений", "Рост реального ВВП"], "target_value": 120, "output_name": "Обслуживание долга (Debt Service)", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -22765,7 +22765,7 @@
       </c>
       <c r="J111" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Алюминий (London Metals Exchange, без премии)", "Коэффициент объема", "Рост реального ВВП", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Коэффициент удельных расходов"], "target_value": 6.82, "output_name": "ICR corr"}</t>
+          <t>{"input_names": ["Алюминий (London Metals Exchange, без премии)", "Коэффициент объема", "Рост реального ВВП", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Коэффициент удельных расходов"], "target_value": 6.82, "output_name": "ICR corr", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -22811,7 +22811,7 @@
       </c>
       <c r="J112" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Цена урана", "Коэффициент постоянных расходов", "Hard Coking Coal (FOB Australia)", "Курс рубля к EUR в конце года (eop EUR/RUB)"], "target_value": 7.82, "output_name": "ISCR (LTM)"}</t>
+          <t>{"input_names": ["Цена урана", "Коэффициент постоянных расходов", "Hard Coking Coal (FOB Australia)", "Курс рубля к EUR в конце года (eop EUR/RUB)"], "target_value": 7.82, "output_name": "ISCR (LTM)", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -22857,7 +22857,7 @@
       </c>
       <c r="J113" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Цена урана", "Коэффициент удельных расходов", "Цена на природный газ на хабе TTF", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)"], "target_value": 3.8, "output_name": "Минимальный годичный ISCR"}</t>
+          <t>{"input_names": ["Цена урана", "Коэффициент удельных расходов", "Цена на природный газ на хабе TTF", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)"], "target_value": 3.8, "output_name": "Минимальный годичный ISCR", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -22903,7 +22903,7 @@
       </c>
       <c r="J114" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Hard Coking Coal (FOB Australia)", "Ставка Euribor 3m"], "target_value": 330, "output_name": "Амортизация"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Hard Coking Coal (FOB Australia)", "Ставка Euribor 3m"], "target_value": 330, "output_name": "Амортизация", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -22949,7 +22949,7 @@
       </c>
       <c r="J115" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Хлорид калия (CFR Ю-В Азия)", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Золото (London Metals Exchange)"], "target_value": 900, "output_name": "Свободный денежный поток (FCFF)"}</t>
+          <t>{"input_names": ["Хлорид калия (CFR Ю-В Азия)", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Золото (London Metals Exchange)"], "target_value": 900, "output_name": "Свободный денежный поток (FCFF)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="J116" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Цена на природный газ на хабе Henry Hub", "Метанол", "Коэффициент удельных расходов", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)"], "target_value": 2.22, "output_name": "Debt/EBITDA"}</t>
+          <t>{"input_names": ["Цена на природный газ на хабе Henry Hub", "Метанол", "Коэффициент удельных расходов", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)"], "target_value": 2.22, "output_name": "Debt/EBITDA", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -23041,7 +23041,7 @@
       </c>
       <c r="J117" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Цена урана", "Ставка Euribor 3m", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Курс рубля к доллару США в конце года (eop USD/RUB)"], "target_value": 18.12, "output_name": "ICR corr"}</t>
+          <t>{"input_names": ["Цена урана", "Ставка Euribor 3m", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Курс рубля к доллару США в конце года (eop USD/RUB)"], "target_value": 18.12, "output_name": "ICR corr", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -23087,7 +23087,7 @@
       </c>
       <c r="J118" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Средний за период курс рубля к доллару США (av USD/RUB)", "Золото (London Metals Exchange)", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Коэффициент объема"], "target_value": 310, "output_name": "Амортизация"}</t>
+          <t>{"input_names": ["Средний за период курс рубля к доллару США (av USD/RUB)", "Золото (London Metals Exchange)", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Коэффициент объема"], "target_value": 310, "output_name": "Амортизация", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -23133,7 +23133,7 @@
       </c>
       <c r="J119" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент постоянных расходов", "Бензол, CFR Япония", "Медь (London Metals Exchange)", "Карбамид (FOB Южный)"], "target_value": 6.44, "output_name": "Коэффициент покрытия процентов в i-ом периоде (ISCR)"}</t>
+          <t>{"input_names": ["Коэффициент постоянных расходов", "Бензол, CFR Япония", "Медь (London Metals Exchange)", "Карбамид (FOB Южный)"], "target_value": 6.44, "output_name": "Коэффициент покрытия процентов в i-ом периоде (ISCR)", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -23179,7 +23179,7 @@
       </c>
       <c r="J120" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент капитальных вложений", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Ставка налога на прибыль организаций", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Никель (London Metals Exchange)"], "target_value": 8.2, "output_name": "ICR corr (LTM)"}</t>
+          <t>{"input_names": ["Коэффициент капитальных вложений", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Ставка налога на прибыль организаций", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Никель (London Metals Exchange)"], "target_value": 8.2, "output_name": "ICR corr (LTM)", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -23225,7 +23225,7 @@
       </c>
       <c r="J121" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Средний за период курс рубля к доллару США (av USD/RUB)", "Коэффициент капитальных вложений", "Карбамид (FOB Южный)"], "target_value": 4300, "output_name": "Выручка"}</t>
+          <t>{"input_names": ["Средний за период курс рубля к доллару США (av USD/RUB)", "Коэффициент капитальных вложений", "Карбамид (FOB Южный)"], "target_value": 4300, "output_name": "Выручка", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -23271,7 +23271,7 @@
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Никель (London Metals Exchange)", "Бензол, CFR Япония", "Железная руда (Iron Ore 62%, CFR China)"], "target_value": 2.42, "output_name": "Минимальный годичный ISCR"}</t>
+          <t>{"input_names": ["Никель (London Metals Exchange)", "Бензол, CFR Япония", "Железная руда (Iron Ore 62%, CFR China)"], "target_value": 2.42, "output_name": "Минимальный годичный ISCR", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -23317,7 +23317,7 @@
       </c>
       <c r="J123" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Нефть марки Urals", "Ставка Libor 3m", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Коэффициент капитальных вложений"], "target_value": 0.244, "output_name": "Рентабельность EBITDA"}</t>
+          <t>{"input_names": ["Нефть марки Urals", "Ставка Libor 3m", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Коэффициент капитальных вложений"], "target_value": 0.244, "output_name": "Рентабельность EBITDA", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -23363,7 +23363,7 @@
       </c>
       <c r="J124" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Hard Coking Coal (FOB Australia)", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Коэффициент цены"], "target_value": 1250, "output_name": "Остаток денежных средств на конец периода"}</t>
+          <t>{"input_names": ["Hard Coking Coal (FOB Australia)", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Коэффициент цены"], "target_value": 1250, "output_name": "Остаток денежных средств на конец периода", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -23409,7 +23409,7 @@
       </c>
       <c r="J125" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Hard Coking Coal (FOB Australia)", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Этилен, CFR Китай", "Бензол, CFR Япония", "Хлорид калия (CFR Ю-В Азия)"], "target_value": 250, "output_name": "Сумма капитальных затрат (CAPEX)"}</t>
+          <t>{"input_names": ["Hard Coking Coal (FOB Australia)", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Этилен, CFR Китай", "Бензол, CFR Япония", "Хлорид калия (CFR Ю-В Азия)"], "target_value": 250, "output_name": "Сумма капитальных затрат (CAPEX)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -23455,7 +23455,7 @@
       </c>
       <c r="J126" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ставка налога на прибыль организаций", "Hard Coking Coal (FOB Australia)", "Нефть марки Brent", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)"], "target_value": 5600, "output_name": "Выручка"}</t>
+          <t>{"input_names": ["Ставка налога на прибыль организаций", "Hard Coking Coal (FOB Australia)", "Нефть марки Brent", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)"], "target_value": 5600, "output_name": "Выручка", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -23501,7 +23501,7 @@
       </c>
       <c r="J127" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["ECB policy rate (Main Refinancing Operations rate)", "Курс рубля к доллару США в конце года (eop USD/RUB)", "Аммиак (FOB Черное море)", "Коэффициент цены", "Ставка Libor 3m"], "target_value": 0.161, "output_name": "Рентабельность EBITDA (LTM)"}</t>
+          <t>{"input_names": ["ECB policy rate (Main Refinancing Operations rate)", "Курс рубля к доллару США в конце года (eop USD/RUB)", "Аммиак (FOB Черное море)", "Коэффициент цены", "Ставка Libor 3m"], "target_value": 0.161, "output_name": "Рентабельность EBITDA (LTM)", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -23547,7 +23547,7 @@
       </c>
       <c r="J128" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент капитальных вложений", "Этилен, CFR Китай", "Курс рубля к доллару США в конце года (eop USD/RUB)", "Средний за период курс рубля к доллару США (av USD/RUB)", "Алюминий (London Metals Exchange, без премии)"], "target_value": 6.45, "output_name": "ICR corr (LTM)"}</t>
+          <t>{"input_names": ["Коэффициент капитальных вложений", "Этилен, CFR Китай", "Курс рубля к доллару США в конце года (eop USD/RUB)", "Средний за период курс рубля к доллару США (av USD/RUB)", "Алюминий (London Metals Exchange, без премии)"], "target_value": 6.45, "output_name": "ICR corr (LTM)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -23593,7 +23593,7 @@
       </c>
       <c r="J129" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Аммиак (FOB Черное море)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "ECB policy rate (Main Refinancing Operations rate)", "Метанол"], "target_value": 7.33, "output_name": "ISCR (LTM)"}</t>
+          <t>{"input_names": ["Аммиак (FOB Черное море)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "ECB policy rate (Main Refinancing Operations rate)", "Метанол"], "target_value": 7.33, "output_name": "ISCR (LTM)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -23639,7 +23639,7 @@
       </c>
       <c r="J130" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Этилен, CFR Китай", "Алюминий (London Metals Exchange, без премии)", "Нефть марки Brent", "Цена на природный газ на хабе Henry Hub", "Ставка налога на прибыль организаций"], "target_value": 1100, "output_name": "EBITDA"}</t>
+          <t>{"input_names": ["Этилен, CFR Китай", "Алюминий (London Metals Exchange, без премии)", "Нефть марки Brent", "Цена на природный газ на хабе Henry Hub", "Ставка налога на прибыль организаций"], "target_value": 1100, "output_name": "EBITDA", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -23685,7 +23685,7 @@
       </c>
       <c r="J131" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Алюминий (London Metals Exchange, без премии)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Курс рубля к доллару США в конце года (eop USD/RUB)"], "target_value": -280, "output_name": "Денежные потоки от финансовых операций (CFF)"}</t>
+          <t>{"input_names": ["Алюминий (London Metals Exchange, без премии)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Курс рубля к доллару США в конце года (eop USD/RUB)"], "target_value": -280, "output_name": "Денежные потоки от финансовых операций (CFF)", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -23731,7 +23731,7 @@
       </c>
       <c r="J132" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Бензол, CFR Япония", "Медь (London Metals Exchange)"], "target_value": 200, "output_name": "Сумма капитальных затрат (CAPEX)"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Бензол, CFR Япония", "Медь (London Metals Exchange)"], "target_value": 200, "output_name": "Сумма капитальных затрат (CAPEX)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
       </c>
       <c r="J133" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент постоянных расходов", "Цена урана", "ECB policy rate (Main Refinancing Operations rate)", "Рост реального ВВП", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)"], "target_value": -250, "output_name": "Чистый денежный поток за период (NCF)"}</t>
+          <t>{"input_names": ["Коэффициент постоянных расходов", "Цена урана", "ECB policy rate (Main Refinancing Operations rate)", "Рост реального ВВП", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)"], "target_value": -250, "output_name": "Чистый денежный поток за период (NCF)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -23823,7 +23823,7 @@
       </c>
       <c r="J134" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Hard Coking Coal (FOB Australia)", "Рост реального ВВП"], "target_value": 4050, "output_name": "Выручка"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Hard Coking Coal (FOB Australia)", "Рост реального ВВП"], "target_value": 4050, "output_name": "Выручка", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -23869,7 +23869,7 @@
       </c>
       <c r="J135" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Никель (London Metals Exchange)", "ECB policy rate (Main Refinancing Operations rate)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Карбамид (FOB Южный)", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": -180, "output_name": "Денежные потоки от инвестиционных операций (CFI)"}</t>
+          <t>{"input_names": ["Никель (London Metals Exchange)", "ECB policy rate (Main Refinancing Operations rate)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Карбамид (FOB Южный)", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": -180, "output_name": "Денежные потоки от инвестиционных операций (CFI)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -23915,7 +23915,7 @@
       </c>
       <c r="J136" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ключевая ставка на конец года (eop)", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Ставка налога на прибыль организаций"], "target_value": 1200, "output_name": "Остаток денежных средств на конец периода"}</t>
+          <t>{"input_names": ["Ключевая ставка на конец года (eop)", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Ставка налога на прибыль организаций"], "target_value": 1200, "output_name": "Остаток денежных средств на конец периода", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -23961,7 +23961,7 @@
       </c>
       <c r="J137" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Никель (London Metals Exchange)", "Коэффициент объема", "Цена на природный газ на хабе Henry Hub"], "target_value": 2.3, "output_name": "Net Debt/EBITDA (LTM)"}</t>
+          <t>{"input_names": ["Никель (London Metals Exchange)", "Коэффициент объема", "Цена на природный газ на хабе Henry Hub"], "target_value": 2.3, "output_name": "Net Debt/EBITDA (LTM)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -24007,7 +24007,7 @@
       </c>
       <c r="J138" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Алюминий (London Metals Exchange, без премии)", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Коэффициент постоянных расходов", "Нефть марки Brent"], "target_value": 290, "output_name": "Амортизация"}</t>
+          <t>{"input_names": ["Алюминий (London Metals Exchange, без премии)", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Коэффициент постоянных расходов", "Нефть марки Brent"], "target_value": 290, "output_name": "Амортизация", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -24053,7 +24053,7 @@
       </c>
       <c r="J139" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ставка налога на прибыль организаций", "Золото (London Metals Exchange)", "Коэффициент цены", "Ключевая ставка на конец года (eop)", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)"], "target_value": 440, "output_name": "Чистый денежный поток за период (NCF)"}</t>
+          <t>{"input_names": ["Ставка налога на прибыль организаций", "Золото (London Metals Exchange)", "Коэффициент цены", "Ключевая ставка на конец года (eop)", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)"], "target_value": 440, "output_name": "Чистый денежный поток за период (NCF)", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -24099,7 +24099,7 @@
       </c>
       <c r="J140" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Цена на природный газ на хабе TTF", "Коэффициент капитальных вложений", "Коэффициент постоянных расходов"], "target_value": 1200, "output_name": "Остаток денежных средств на конец периода"}</t>
+          <t>{"input_names": ["Цена на природный газ на хабе TTF", "Коэффициент капитальных вложений", "Коэффициент постоянных расходов"], "target_value": 1200, "output_name": "Остаток денежных средств на конец периода", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -24145,7 +24145,7 @@
       </c>
       <c r="J141" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Алюминий (London Metals Exchange, без премии)", "Медь (London Metals Exchange)", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": 4850, "output_name": "Выручка (LTM)"}</t>
+          <t>{"input_names": ["Алюминий (London Metals Exchange, без премии)", "Медь (London Metals Exchange)", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": 4850, "output_name": "Выручка (LTM)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -24191,7 +24191,7 @@
       </c>
       <c r="J142" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Медь (London Metals Exchange)", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Курс рубля к EUR в конце года (eop EUR/RUB)"], "target_value": 4500, "output_name": "Выручка (LTM)"}</t>
+          <t>{"input_names": ["Медь (London Metals Exchange)", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Курс рубля к EUR в конце года (eop EUR/RUB)"], "target_value": 4500, "output_name": "Выручка (LTM)", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -24237,7 +24237,7 @@
       </c>
       <c r="J143" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент капитальных вложений", "Алюминий (London Metals Exchange, без премии)", "Ключевая ставка на конец года (eop)", "Хлорид калия (CFR Ю-В Азия)", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)"], "target_value": 1200, "output_name": "EBITDA"}</t>
+          <t>{"input_names": ["Коэффициент капитальных вложений", "Алюминий (London Metals Exchange, без премии)", "Ключевая ставка на конец года (eop)", "Хлорид калия (CFR Ю-В Азия)", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)"], "target_value": 1200, "output_name": "EBITDA", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -24283,7 +24283,7 @@
       </c>
       <c r="J144" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Железная руда (Iron Ore 62%, CFR China)", "Коэффициент постоянных расходов", "Алюминий (London Metals Exchange, без премии)"], "target_value": 0.75, "output_name": "Net Debt/EBITDA"}</t>
+          <t>{"input_names": ["Железная руда (Iron Ore 62%, CFR China)", "Коэффициент постоянных расходов", "Алюминий (London Metals Exchange, без премии)"], "target_value": 0.75, "output_name": "Net Debt/EBITDA", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -24329,7 +24329,7 @@
       </c>
       <c r="J145" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Коэффициент цены", "Ставка Euribor 3m", "Хлорид калия (CFR Ю-В Азия)"], "target_value": 600, "output_name": "Долг (Debt)"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Коэффициент цены", "Ставка Euribor 3m", "Хлорид калия (CFR Ю-В Азия)"], "target_value": 600, "output_name": "Долг (Debt)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -24375,7 +24375,7 @@
       </c>
       <c r="J146" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Нефть марки Urals", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Нефть марки Brent", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Карбамид (FOB Южный)"], "target_value": 2.43, "output_name": "Минимальный годичный DSCR"}</t>
+          <t>{"input_names": ["Нефть марки Urals", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Нефть марки Brent", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Карбамид (FOB Южный)"], "target_value": 2.43, "output_name": "Минимальный годичный DSCR", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -24421,7 +24421,7 @@
       </c>
       <c r="J147" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Цена на природный газ на хабе Henry Hub", "Курс рубля к EUR в конце года (eop EUR/RUB)", "ECB policy rate (Main Refinancing Operations rate)", "Ставка Libor 3m", "Этилен, CFR Китай"], "target_value": 170, "output_name": "Платежи процентов по долговым обязательствам "}</t>
+          <t>{"input_names": ["Цена на природный газ на хабе Henry Hub", "Курс рубля к EUR в конце года (eop EUR/RUB)", "ECB policy rate (Main Refinancing Operations rate)", "Ставка Libor 3m", "Этилен, CFR Китай"], "target_value": 170, "output_name": "Платежи процентов по долговым обязательствам ", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -24467,7 +24467,7 @@
       </c>
       <c r="J148" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Цена на природный газ на хабе TTF", "Нефть марки Brent", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Хлорид калия (CFR Ю-В Азия)"], "target_value": -180, "output_name": "Денежные потоки от инвестиционных операций (CFI)"}</t>
+          <t>{"input_names": ["Цена на природный газ на хабе TTF", "Нефть марки Brent", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Хлорид калия (CFR Ю-В Азия)"], "target_value": -180, "output_name": "Денежные потоки от инвестиционных операций (CFI)", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -24513,7 +24513,7 @@
       </c>
       <c r="J149" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Метанол", "Рост реального ВВП", "Никель (London Metals Exchange)"], "target_value": 0.212, "output_name": "Рентабельность EBITDA (LTM)"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Метанол", "Рост реального ВВП", "Никель (London Metals Exchange)"], "target_value": 0.212, "output_name": "Рентабельность EBITDA (LTM)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -24559,7 +24559,7 @@
       </c>
       <c r="J150" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Железная руда (Iron Ore 62%, CFR China)", "Этилен, CFR Китай", "Курс рубля к доллару США в конце года (eop USD/RUB)", "Метанол"], "target_value": 2.17, "output_name": "Минимальный годичный ISCR"}</t>
+          <t>{"input_names": ["Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Железная руда (Iron Ore 62%, CFR China)", "Этилен, CFR Китай", "Курс рубля к доллару США в конце года (eop USD/RUB)", "Метанол"], "target_value": 2.17, "output_name": "Минимальный годичный ISCR", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -24605,7 +24605,7 @@
       </c>
       <c r="J151" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Нефть марки Brent", "Железная руда (Iron Ore 62%, CFR China)", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Цена урана"], "target_value": 580, "output_name": "Чистый долг (Net Debt)"}</t>
+          <t>{"input_names": ["Нефть марки Brent", "Железная руда (Iron Ore 62%, CFR China)", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Цена урана"], "target_value": 580, "output_name": "Чистый долг (Net Debt)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -24651,7 +24651,7 @@
       </c>
       <c r="J152" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Карбамид (FOB Южный)", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Нефть марки Urals", "Коэффициент объема"], "target_value": 9.17, "output_name": "Коэффициент покрытия процентов в i-ом периоде (ICR)"}</t>
+          <t>{"input_names": ["Карбамид (FOB Южный)", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Нефть марки Urals", "Коэффициент объема"], "target_value": 9.17, "output_name": "Коэффициент покрытия процентов в i-ом периоде (ICR)", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -24697,7 +24697,7 @@
       </c>
       <c r="J153" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент объема", "Медь (London Metals Exchange)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)"], "target_value": 0.125, "output_name": "Рентабельность чистой прибыли"}</t>
+          <t>{"input_names": ["Коэффициент объема", "Медь (London Metals Exchange)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)"], "target_value": 0.125, "output_name": "Рентабельность чистой прибыли", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -24743,7 +24743,7 @@
       </c>
       <c r="J154" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Никель (London Metals Exchange)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Ставка Euribor 3m"], "target_value": 8.03, "output_name": "ICR corr (LTM)"}</t>
+          <t>{"input_names": ["Никель (London Metals Exchange)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Ставка Euribor 3m"], "target_value": 8.03, "output_name": "ICR corr (LTM)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -24789,7 +24789,7 @@
       </c>
       <c r="J155" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Золото (London Metals Exchange)", "Цена урана", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Цена на природный газ на хабе Henry Hub"], "target_value": 2150, "output_name": "Остаток денежных средств на конец периода"}</t>
+          <t>{"input_names": ["Золото (London Metals Exchange)", "Цена урана", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Цена на природный газ на хабе Henry Hub"], "target_value": 2150, "output_name": "Остаток денежных средств на конец периода", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -24835,7 +24835,7 @@
       </c>
       <c r="J156" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Железная руда (Iron Ore 62%, CFR China)", "Ключевая ставка на конец года (eop)", "Карбамид (FOB Южный)"], "target_value": 240, "output_name": "Сумма капитальных затрат (CAPEX)"}</t>
+          <t>{"input_names": ["Железная руда (Iron Ore 62%, CFR China)", "Ключевая ставка на конец года (eop)", "Карбамид (FOB Южный)"], "target_value": 240, "output_name": "Сумма капитальных затрат (CAPEX)", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -24881,7 +24881,7 @@
       </c>
       <c r="J157" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Цена на природный газ на хабе TTF", "Аммиак (FOB Черное море)", "Золото (London Metals Exchange)", "Коэффициент постоянных расходов"], "target_value": -280, "output_name": "Денежные потоки от финансовых операций (CFF)"}</t>
+          <t>{"input_names": ["Цена на природный газ на хабе TTF", "Аммиак (FOB Черное море)", "Золото (London Metals Exchange)", "Коэффициент постоянных расходов"], "target_value": -280, "output_name": "Денежные потоки от финансовых операций (CFF)", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -24927,7 +24927,7 @@
       </c>
       <c r="J158" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Никель (London Metals Exchange)", "Этилен, CFR Китай", "ECB policy rate (Main Refinancing Operations rate)"], "target_value": 4000, "output_name": "Выручка"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Никель (London Metals Exchange)", "Этилен, CFR Китай", "ECB policy rate (Main Refinancing Operations rate)"], "target_value": 4000, "output_name": "Выручка", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -24973,7 +24973,7 @@
       </c>
       <c r="J159" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Алюминий (London Metals Exchange, без премии)", "Этилен, CFR Китай", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Карбамид (FOB Южный)", "Коэффициент удельных расходов"], "target_value": 10.53, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)"}</t>
+          <t>{"input_names": ["Алюминий (London Metals Exchange, без премии)", "Этилен, CFR Китай", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Карбамид (FOB Южный)", "Коэффициент удельных расходов"], "target_value": 10.53, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -25019,7 +25019,7 @@
       </c>
       <c r="J160" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент цены", "Цена на природный газ на хабе TTF", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Ставка налога на прибыль организаций"], "target_value": 0.156, "output_name": "Рентабельность EBITDA"}</t>
+          <t>{"input_names": ["Коэффициент цены", "Цена на природный газ на хабе TTF", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Ставка налога на прибыль организаций"], "target_value": 0.156, "output_name": "Рентабельность EBITDA", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -25065,7 +25065,7 @@
       </c>
       <c r="J161" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Хлорид калия (CFR Ю-В Азия)", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Медь (London Metals Exchange)"], "target_value": 6050, "output_name": "Выручка"}</t>
+          <t>{"input_names": ["Хлорид калия (CFR Ю-В Азия)", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Медь (London Metals Exchange)"], "target_value": 6050, "output_name": "Выручка", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -25111,7 +25111,7 @@
       </c>
       <c r="J162" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент капитальных вложений", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Средний за период курс рубля к доллару США (av USD/RUB)", "Железная руда (Iron Ore 62%, CFR China)", "Метанол"], "target_value": 350, "output_name": "Чистая прибыль"}</t>
+          <t>{"input_names": ["Коэффициент капитальных вложений", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Средний за период курс рубля к доллару США (av USD/RUB)", "Железная руда (Iron Ore 62%, CFR China)", "Метанол"], "target_value": 350, "output_name": "Чистая прибыль", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -25157,7 +25157,7 @@
       </c>
       <c r="J163" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ставка Libor 3m", "Hard Coking Coal (FOB Australia)", "Коэффициент капитальных вложений"], "target_value": 6.64, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)"}</t>
+          <t>{"input_names": ["Ставка Libor 3m", "Hard Coking Coal (FOB Australia)", "Коэффициент капитальных вложений"], "target_value": 6.64, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="J164" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Коэффициент постоянных расходов", "Бензол, CFR Япония"], "target_value": 1200, "output_name": "Остаток денежных средств на конец периода"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Коэффициент постоянных расходов", "Бензол, CFR Япония"], "target_value": 1200, "output_name": "Остаток денежных средств на конец периода", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -25249,7 +25249,7 @@
       </c>
       <c r="J165" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Нефть марки Brent", "Нефть марки Urals", "Метанол", "Аммиак (FOB Черное море)", "Бензол, CFR Япония"], "target_value": 2.28, "output_name": "Минимальный годичный ISCR"}</t>
+          <t>{"input_names": ["Нефть марки Brent", "Нефть марки Urals", "Метанол", "Аммиак (FOB Черное море)", "Бензол, CFR Япония"], "target_value": 2.28, "output_name": "Минимальный годичный ISCR", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -25295,7 +25295,7 @@
       </c>
       <c r="J166" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Карбамид (FOB Южный)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Коэффициент цены"], "target_value": 0.38, "output_name": "Net Debt/EBITDA"}</t>
+          <t>{"input_names": ["Карбамид (FOB Южный)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Коэффициент цены"], "target_value": 0.38, "output_name": "Net Debt/EBITDA", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -25341,7 +25341,7 @@
       </c>
       <c r="J167" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Хлорид калия (CFR Ю-В Азия)", "Метанол", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)"], "target_value": 4950, "output_name": "Выручка (LTM)"}</t>
+          <t>{"input_names": ["Хлорид калия (CFR Ю-В Азия)", "Метанол", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)"], "target_value": 4950, "output_name": "Выручка (LTM)", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -25387,7 +25387,7 @@
       </c>
       <c r="J168" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент удельных расходов", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Метанол", "Бензол, CFR Япония"], "target_value": 7.19, "output_name": "ICR corr"}</t>
+          <t>{"input_names": ["Коэффициент удельных расходов", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Метанол", "Бензол, CFR Япония"], "target_value": 7.19, "output_name": "ICR corr", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -25433,7 +25433,7 @@
       </c>
       <c r="J169" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Аммиак (FOB Черное море)", "Золото (London Metals Exchange)"], "target_value": 2.82, "output_name": "Debt/EBITDA"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Аммиак (FOB Черное море)", "Золото (London Metals Exchange)"], "target_value": 2.82, "output_name": "Debt/EBITDA", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -25479,7 +25479,7 @@
       </c>
       <c r="J170" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Железная руда (Iron Ore 62%, CFR China)", "Хлорид калия (CFR Ю-В Азия)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)"], "target_value": 100, "output_name": "Обслуживание долга (Debt Service)"}</t>
+          <t>{"input_names": ["Железная руда (Iron Ore 62%, CFR China)", "Хлорид калия (CFR Ю-В Азия)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)"], "target_value": 100, "output_name": "Обслуживание долга (Debt Service)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -25525,7 +25525,7 @@
       </c>
       <c r="J171" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Аммиак (FOB Черное море)", "Медь (London Metals Exchange)", "Этилен, CFR Китай", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Железная руда (Iron Ore 62%, CFR China)"], "target_value": 0.56, "output_name": "Debt/EBITDA (LTM)"}</t>
+          <t>{"input_names": ["Аммиак (FOB Черное море)", "Медь (London Metals Exchange)", "Этилен, CFR Китай", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Железная руда (Iron Ore 62%, CFR China)"], "target_value": 0.56, "output_name": "Debt/EBITDA (LTM)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -25571,7 +25571,7 @@
       </c>
       <c r="J172" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Аммиак (FOB Черное море)", "Этилен, CFR Китай", "Ключевая ставка на конец года (eop)", "Коэффициент капитальных вложений", "Курс рубля к доллару США в конце года (eop USD/RUB)"], "target_value": 0.162, "output_name": "Рентабельность EBITDA"}</t>
+          <t>{"input_names": ["Аммиак (FOB Черное море)", "Этилен, CFR Китай", "Ключевая ставка на конец года (eop)", "Коэффициент капитальных вложений", "Курс рубля к доллару США в конце года (eop USD/RUB)"], "target_value": 0.162, "output_name": "Рентабельность EBITDA", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -25617,7 +25617,7 @@
       </c>
       <c r="J173" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Бензол, CFR Япония", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Карбамид (FOB Южный)"], "target_value": -340, "output_name": "Денежные потоки от финансовых операций (CFF)"}</t>
+          <t>{"input_names": ["Бензол, CFR Япония", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Карбамид (FOB Южный)"], "target_value": -340, "output_name": "Денежные потоки от финансовых операций (CFF)", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -25663,7 +25663,7 @@
       </c>
       <c r="J174" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Алюминий (London Metals Exchange, без премии)", "Цена на природный газ на хабе TTF", "Медь (London Metals Exchange)", "Никель (London Metals Exchange)", "Коэффициент капитальных вложений"], "target_value": 55, "output_name": "Обслуживание долга (Debt Service)"}</t>
+          <t>{"input_names": ["Алюминий (London Metals Exchange, без премии)", "Цена на природный газ на хабе TTF", "Медь (London Metals Exchange)", "Никель (London Metals Exchange)", "Коэффициент капитальных вложений"], "target_value": 55, "output_name": "Обслуживание долга (Debt Service)", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -25709,7 +25709,7 @@
       </c>
       <c r="J175" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Карбамид (FOB Южный)", "Коэффициент капитальных вложений", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)"], "target_value": 6.0, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)"}</t>
+          <t>{"input_names": ["Карбамид (FOB Южный)", "Коэффициент капитальных вложений", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)"], "target_value": 6.0, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -25755,7 +25755,7 @@
       </c>
       <c r="J176" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Коэффициент цены", "Hard Coking Coal (FOB Australia)"], "target_value": 190, "output_name": "Сумма капитальных затрат (CAPEX)"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Коэффициент цены", "Hard Coking Coal (FOB Australia)"], "target_value": 190, "output_name": "Сумма капитальных затрат (CAPEX)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -25801,7 +25801,7 @@
       </c>
       <c r="J177" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Аммиак (FOB Черное море)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Метанол", "Коэффициент постоянных расходов"], "target_value": 350, "output_name": "Чистая прибыль"}</t>
+          <t>{"input_names": ["Аммиак (FOB Черное море)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Метанол", "Коэффициент постоянных расходов"], "target_value": 350, "output_name": "Чистая прибыль", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -25847,7 +25847,7 @@
       </c>
       <c r="J178" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Нефть марки Urals", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)"], "target_value": 1150, "output_name": "Денежные потоки от текущих операций (CFO)"}</t>
+          <t>{"input_names": ["Нефть марки Urals", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)"], "target_value": 1150, "output_name": "Денежные потоки от текущих операций (CFO)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -25893,7 +25893,7 @@
       </c>
       <c r="J179" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент капитальных вложений", "Этилен, CFR Китай", "Средний за период курс рубля к доллару США (av USD/RUB)", "Курс рубля к доллару США в конце года (eop USD/RUB)"], "target_value": 1.92, "output_name": "Net Debt/EBITDA (LTM)"}</t>
+          <t>{"input_names": ["Коэффициент капитальных вложений", "Этилен, CFR Китай", "Средний за период курс рубля к доллару США (av USD/RUB)", "Курс рубля к доллару США в конце года (eop USD/RUB)"], "target_value": 1.92, "output_name": "Net Debt/EBITDA (LTM)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -25939,7 +25939,7 @@
       </c>
       <c r="J180" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Алюминий (London Metals Exchange, без премии)", "Ставка налога на прибыль организаций", "Нефть марки Urals", "Hard Coking Coal (FOB Australia)", "Хлорид калия (CFR Ю-В Азия)"], "target_value": 0.6, "output_name": "Net Debt/EBITDA"}</t>
+          <t>{"input_names": ["Алюминий (London Metals Exchange, без премии)", "Ставка налога на прибыль организаций", "Нефть марки Urals", "Hard Coking Coal (FOB Australia)", "Хлорид калия (CFR Ю-В Азия)"], "target_value": 0.6, "output_name": "Net Debt/EBITDA", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -25985,7 +25985,7 @@
       </c>
       <c r="J181" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["ECB policy rate (Main Refinancing Operations rate)", "Ставка налога на прибыль организаций", "Hard Coking Coal (FOB Australia)", "Карбамид (FOB Южный)", "Коэффициент удельных расходов"], "target_value": 2.58, "output_name": "Net Debt/EBITDA"}</t>
+          <t>{"input_names": ["ECB policy rate (Main Refinancing Operations rate)", "Ставка налога на прибыль организаций", "Hard Coking Coal (FOB Australia)", "Карбамид (FOB Южный)", "Коэффициент удельных расходов"], "target_value": 2.58, "output_name": "Net Debt/EBITDA", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -26031,7 +26031,7 @@
       </c>
       <c r="J182" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Золото (London Metals Exchange)", "Аммиак (FOB Черное море)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)"], "target_value": 7.02, "output_name": "DSCR (LTM)"}</t>
+          <t>{"input_names": ["Золото (London Metals Exchange)", "Аммиак (FOB Черное море)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)"], "target_value": 7.02, "output_name": "DSCR (LTM)", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -26077,7 +26077,7 @@
       </c>
       <c r="J183" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ставка Euribor 3m", "Этилен, CFR Китай", "Алюминий (London Metals Exchange, без премии)", "Медь (London Metals Exchange)", "Цена на природный газ на хабе Henry Hub"], "target_value": 900, "output_name": "Остаток денежных средств на конец периода"}</t>
+          <t>{"input_names": ["Ставка Euribor 3m", "Этилен, CFR Китай", "Алюминий (London Metals Exchange, без премии)", "Медь (London Metals Exchange)", "Цена на природный газ на хабе Henry Hub"], "target_value": 900, "output_name": "Остаток денежных средств на конец периода", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -26123,7 +26123,7 @@
       </c>
       <c r="J184" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Нефть марки Brent", "Нефть марки Urals", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Коэффициент объема", "Алюминий (London Metals Exchange, без премии)"], "target_value": 7.88, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)"}</t>
+          <t>{"input_names": ["Нефть марки Brent", "Нефть марки Urals", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Коэффициент объема", "Алюминий (London Metals Exchange, без премии)"], "target_value": 7.88, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -26169,7 +26169,7 @@
       </c>
       <c r="J185" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Никель (London Metals Exchange)", "Цена на природный газ на хабе TTF", "Курс рубля к доллару США в конце года (eop USD/RUB)", "Этилен, CFR Китай"], "target_value": 1050, "output_name": "Денежные потоки от текущих операций (CFO)"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Никель (London Metals Exchange)", "Цена на природный газ на хабе TTF", "Курс рубля к доллару США в конце года (eop USD/RUB)", "Этилен, CFR Китай"], "target_value": 1050, "output_name": "Денежные потоки от текущих операций (CFO)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -26215,7 +26215,7 @@
       </c>
       <c r="J186" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Коэффициент постоянных расходов"], "target_value": 0.248, "output_name": "Рентабельность EBITDA (LTM)"}</t>
+          <t>{"input_names": ["Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Коэффициент постоянных расходов"], "target_value": 0.248, "output_name": "Рентабельность EBITDA (LTM)", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -26261,7 +26261,7 @@
       </c>
       <c r="J187" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Железная руда (Iron Ore 62%, CFR China)", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Метанол"], "target_value": 0.075, "output_name": "Рентабельность чистой прибыли"}</t>
+          <t>{"input_names": ["Железная руда (Iron Ore 62%, CFR China)", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Метанол"], "target_value": 0.075, "output_name": "Рентабельность чистой прибыли", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -26307,7 +26307,7 @@
       </c>
       <c r="J188" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Хлорид калия (CFR Ю-В Азия)", "Ставка Libor 3m", "Hard Coking Coal (FOB Australia)", "Никель (London Metals Exchange)"], "target_value": 1850, "output_name": "Остаток денежных средств на конец периода"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Хлорид калия (CFR Ю-В Азия)", "Ставка Libor 3m", "Hard Coking Coal (FOB Australia)", "Никель (London Metals Exchange)"], "target_value": 1850, "output_name": "Остаток денежных средств на конец периода", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -26353,7 +26353,7 @@
       </c>
       <c r="J189" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Нефть марки Brent", "ECB policy rate (Main Refinancing Operations rate)"], "target_value": 1200, "output_name": "EBITDA"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Нефть марки Brent", "ECB policy rate (Main Refinancing Operations rate)"], "target_value": 1200, "output_name": "EBITDA", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -26399,7 +26399,7 @@
       </c>
       <c r="J190" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Золото (London Metals Exchange)", "Никель (London Metals Exchange)", "Коэффициент цены", "ECB policy rate (Main Refinancing Operations rate)"], "target_value": 90, "output_name": "Проценты к уплате"}</t>
+          <t>{"input_names": ["Золото (London Metals Exchange)", "Никель (London Metals Exchange)", "Коэффициент цены", "ECB policy rate (Main Refinancing Operations rate)"], "target_value": 90, "output_name": "Проценты к уплате", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -26445,7 +26445,7 @@
       </c>
       <c r="J191" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Коэффициент постоянных расходов", "Ставка Libor 3m", "ECB policy rate (Main Refinancing Operations rate)", "Железная руда (Iron Ore 62%, CFR China)"], "target_value": 3.67, "output_name": "Минимальный годичный ISCR"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Коэффициент постоянных расходов", "Ставка Libor 3m", "ECB policy rate (Main Refinancing Operations rate)", "Железная руда (Iron Ore 62%, CFR China)"], "target_value": 3.67, "output_name": "Минимальный годичный ISCR", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -26491,7 +26491,7 @@
       </c>
       <c r="J192" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Хлорид калия (CFR Ю-В Азия)", "Нефть марки Urals", "Бензол, CFR Япония", "Нефть марки Brent"], "target_value": 6.24, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)"}</t>
+          <t>{"input_names": ["Хлорид калия (CFR Ю-В Азия)", "Нефть марки Urals", "Бензол, CFR Япония", "Нефть марки Brent"], "target_value": 6.24, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -26537,7 +26537,7 @@
       </c>
       <c r="J193" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Карбамид (FOB Южный)", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Цена урана", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)"], "target_value": 0.26, "output_name": "Рентабельность EBITDA"}</t>
+          <t>{"input_names": ["Карбамид (FOB Южный)", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Цена урана", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)"], "target_value": 0.26, "output_name": "Рентабельность EBITDA", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -26583,7 +26583,7 @@
       </c>
       <c r="J194" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ставка Libor 3m", "Коэффициент удельных расходов", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Этилен, CFR Китай", "Аммиак (FOB Черное море)"], "target_value": 750, "output_name": "Денежные средства, доступные для обслуживания долга (CFADS)"}</t>
+          <t>{"input_names": ["Ставка Libor 3m", "Коэффициент удельных расходов", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Этилен, CFR Китай", "Аммиак (FOB Черное море)"], "target_value": 750, "output_name": "Денежные средства, доступные для обслуживания долга (CFADS)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -26629,7 +26629,7 @@
       </c>
       <c r="J195" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Карбамид (FOB Южный)", "Коэффициент постоянных расходов", "Коэффициент капитальных вложений"], "target_value": 2850, "output_name": "Долг (Debt)"}</t>
+          <t>{"input_names": ["Карбамид (FOB Южный)", "Коэффициент постоянных расходов", "Коэффициент капитальных вложений"], "target_value": 2850, "output_name": "Долг (Debt)", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -26675,7 +26675,7 @@
       </c>
       <c r="J196" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Медь (London Metals Exchange)", "Коэффициент удельных расходов", "Никель (London Metals Exchange)", "Этилен, CFR Китай"], "target_value": 1.85, "output_name": "Debt/EBITDA (LTM)"}</t>
+          <t>{"input_names": ["Медь (London Metals Exchange)", "Коэффициент удельных расходов", "Никель (London Metals Exchange)", "Этилен, CFR Китай"], "target_value": 1.85, "output_name": "Debt/EBITDA (LTM)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -26721,7 +26721,7 @@
       </c>
       <c r="J197" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент цены", "Курс рубля к доллару США в конце года (eop USD/RUB)", "Нефть марки Brent", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Ставка налога на прибыль организаций"], "target_value": 4.59, "output_name": "ICR corr (LTM)"}</t>
+          <t>{"input_names": ["Коэффициент цены", "Курс рубля к доллару США в конце года (eop USD/RUB)", "Нефть марки Brent", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Ставка налога на прибыль организаций"], "target_value": 4.59, "output_name": "ICR corr (LTM)", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -26767,7 +26767,7 @@
       </c>
       <c r="J198" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Хлорид калия (CFR Ю-В Азия)", "Железная руда (Iron Ore 62%, CFR China)", "Цена на природный газ на хабе Henry Hub"], "target_value": 220, "output_name": "Сумма капитальных затрат (CAPEX)"}</t>
+          <t>{"input_names": ["Хлорид калия (CFR Ю-В Азия)", "Железная руда (Iron Ore 62%, CFR China)", "Цена на природный газ на хабе Henry Hub"], "target_value": 220, "output_name": "Сумма капитальных затрат (CAPEX)", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -26813,7 +26813,7 @@
       </c>
       <c r="J199" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Хлорид калия (CFR Ю-В Азия)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Бензол, CFR Япония"], "target_value": 2.73, "output_name": "Минимальный годичный DSCR"}</t>
+          <t>{"input_names": ["Хлорид калия (CFR Ю-В Азия)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Бензол, CFR Япония"], "target_value": 2.73, "output_name": "Минимальный годичный DSCR", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -26859,7 +26859,7 @@
       </c>
       <c r="J200" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Коэффициент удельных расходов", "Коэффициент капитальных вложений", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Курс рубля к EUR в конце года (eop EUR/RUB)"], "target_value": 0.28, "output_name": "Рентабельность EBITDA (LTM)"}</t>
+          <t>{"input_names": ["Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Коэффициент удельных расходов", "Коэффициент капитальных вложений", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Курс рубля к EUR в конце года (eop EUR/RUB)"], "target_value": 0.28, "output_name": "Рентабельность EBITDA (LTM)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -26905,7 +26905,7 @@
       </c>
       <c r="J201" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Курс рубля к EUR в конце года (eop EUR/RUB)", "Цена на природный газ на хабе TTF", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Железная руда (Iron Ore 62%, CFR China)", "Коэффициент цены"], "target_value": 7.78, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)"}</t>
+          <t>{"input_names": ["Курс рубля к EUR в конце года (eop EUR/RUB)", "Цена на природный газ на хабе TTF", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Железная руда (Iron Ore 62%, CFR China)", "Коэффициент цены"], "target_value": 7.78, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -26951,7 +26951,7 @@
       </c>
       <c r="J202" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Железная руда (Iron Ore 62%, CFR China)", "Коэффициент удельных расходов", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Хлорид калия (CFR Ю-В Азия)", "Курс рубля к доллару США в конце года (eop USD/RUB)"], "target_value": 7.55, "output_name": "DSCR (LTM)"}</t>
+          <t>{"input_names": ["Железная руда (Iron Ore 62%, CFR China)", "Коэффициент удельных расходов", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Хлорид калия (CFR Ю-В Азия)", "Курс рубля к доллару США в конце года (eop USD/RUB)"], "target_value": 7.55, "output_name": "DSCR (LTM)", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -26997,7 +26997,7 @@
       </c>
       <c r="J203" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Цена урана", "Алюминий (London Metals Exchange, без премии)", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)"], "target_value": 1600, "output_name": "Долг (Debt)"}</t>
+          <t>{"input_names": ["Цена урана", "Алюминий (London Metals Exchange, без премии)", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)"], "target_value": 1600, "output_name": "Долг (Debt)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -27043,7 +27043,7 @@
       </c>
       <c r="J204" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ставка Euribor 3m", "Курс рубля к доллару США в конце года (eop USD/RUB)", "Никель (London Metals Exchange)"], "target_value": 8.26, "output_name": "ICR corr (LTM)"}</t>
+          <t>{"input_names": ["Ставка Euribor 3m", "Курс рубля к доллару США в конце года (eop USD/RUB)", "Никель (London Metals Exchange)"], "target_value": 8.26, "output_name": "ICR corr (LTM)", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -27089,7 +27089,7 @@
       </c>
       <c r="J205" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент постоянных расходов", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Коэффициент капитальных вложений"], "target_value": 3.81, "output_name": "Минимальный годичный ISCR"}</t>
+          <t>{"input_names": ["Коэффициент постоянных расходов", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Коэффициент капитальных вложений"], "target_value": 3.81, "output_name": "Минимальный годичный ISCR", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -27135,7 +27135,7 @@
       </c>
       <c r="J206" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Цена на природный газ на хабе Henry Hub", "Карбамид (FOB Южный)"], "target_value": 8.73, "output_name": "Коэффициент покрытия процентов в i-ом периоде (ISCR)"}</t>
+          <t>{"input_names": ["Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Цена на природный газ на хабе Henry Hub", "Карбамид (FOB Южный)"], "target_value": 8.73, "output_name": "Коэффициент покрытия процентов в i-ом периоде (ISCR)", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -27181,7 +27181,7 @@
       </c>
       <c r="J207" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Этилен, CFR Китай", "ECB policy rate (Main Refinancing Operations rate)"], "target_value": -1250, "output_name": "Денежные потоки от финансовых операций (CFF)"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Этилен, CFR Китай", "ECB policy rate (Main Refinancing Operations rate)"], "target_value": -1250, "output_name": "Денежные потоки от финансовых операций (CFF)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -27227,7 +27227,7 @@
       </c>
       <c r="J208" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Метанол", "Коэффициент капитальных вложений", "Средний за период курс рубля к доллару США (av USD/RUB)", "Железная руда (Iron Ore 62%, CFR China)"], "target_value": 9.33, "output_name": "ICR corr (LTM)"}</t>
+          <t>{"input_names": ["Метанол", "Коэффициент капитальных вложений", "Средний за период курс рубля к доллару США (av USD/RUB)", "Железная руда (Iron Ore 62%, CFR China)"], "target_value": 9.33, "output_name": "ICR corr (LTM)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -27273,7 +27273,7 @@
       </c>
       <c r="J209" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ставка Euribor 3m", "Hard Coking Coal (FOB Australia)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)"], "target_value": 450, "output_name": "Чистая прибыль"}</t>
+          <t>{"input_names": ["Ставка Euribor 3m", "Hard Coking Coal (FOB Australia)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)"], "target_value": 450, "output_name": "Чистая прибыль", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -27319,7 +27319,7 @@
       </c>
       <c r="J210" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Ключевая ставка на конец года (eop)", "Курс рубля к EUR в конце года (eop EUR/RUB)"], "target_value": 750, "output_name": "Долг (Debt)"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Ключевая ставка на конец года (eop)", "Курс рубля к EUR в конце года (eop EUR/RUB)"], "target_value": 750, "output_name": "Долг (Debt)", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -27365,7 +27365,7 @@
       </c>
       <c r="J211" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Цена на природный газ на хабе TTF", "ECB policy rate (Main Refinancing Operations rate)", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": 1250, "output_name": "EBITDA"}</t>
+          <t>{"input_names": ["Цена на природный газ на хабе TTF", "ECB policy rate (Main Refinancing Operations rate)", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": 1250, "output_name": "EBITDA", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -27411,7 +27411,7 @@
       </c>
       <c r="J212" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Золото (London Metals Exchange)", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)"], "target_value": 650, "output_name": "Свободный денежный поток (FCFF)"}</t>
+          <t>{"input_names": ["Золото (London Metals Exchange)", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)"], "target_value": 650, "output_name": "Свободный денежный поток (FCFF)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -27457,7 +27457,7 @@
       </c>
       <c r="J213" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Hard Coking Coal (FOB Australia)", "Цена на природный газ на хабе Henry Hub"], "target_value": 4000, "output_name": "Выручка"}</t>
+          <t>{"input_names": ["Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Hard Coking Coal (FOB Australia)", "Цена на природный газ на хабе Henry Hub"], "target_value": 4000, "output_name": "Выручка", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -27503,7 +27503,7 @@
       </c>
       <c r="J214" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Железная руда (Iron Ore 62%, CFR China)", "Метанол", "Hard Coking Coal (FOB Australia)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Ставка налога на прибыль организаций"], "target_value": 0.259, "output_name": "Рентабельность EBITDA"}</t>
+          <t>{"input_names": ["Железная руда (Iron Ore 62%, CFR China)", "Метанол", "Hard Coking Coal (FOB Australia)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Ставка налога на прибыль организаций"], "target_value": 0.259, "output_name": "Рентабельность EBITDA", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -27549,7 +27549,7 @@
       </c>
       <c r="J215" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Золото (London Metals Exchange)", "Коэффициент удельных расходов", "Цена урана", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Цена на природный газ на хабе Henry Hub"], "target_value": 90, "output_name": "Проценты к уплате"}</t>
+          <t>{"input_names": ["Золото (London Metals Exchange)", "Коэффициент удельных расходов", "Цена урана", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Цена на природный газ на хабе Henry Hub"], "target_value": 90, "output_name": "Проценты к уплате", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -27595,7 +27595,7 @@
       </c>
       <c r="J216" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Карбамид (FOB Южный)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Нефть марки Brent", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Цена на природный газ на хабе Henry Hub"], "target_value": 950, "output_name": "Остаток денежных средств на конец периода"}</t>
+          <t>{"input_names": ["Карбамид (FOB Южный)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Нефть марки Brent", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Цена на природный газ на хабе Henry Hub"], "target_value": 950, "output_name": "Остаток денежных средств на конец периода", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -27641,7 +27641,7 @@
       </c>
       <c r="J217" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Цена урана", "Ключевая ставка на конец года (eop)", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Курс рубля к EUR в конце года (eop EUR/RUB)"], "target_value": 1.37, "output_name": "Debt/EBITDA"}</t>
+          <t>{"input_names": ["Цена урана", "Ключевая ставка на конец года (eop)", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Курс рубля к EUR в конце года (eop EUR/RUB)"], "target_value": 1.37, "output_name": "Debt/EBITDA", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="J218" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Рост реального ВВП", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Хлорид калия (CFR Ю-В Азия)", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)"], "target_value": 7.73, "output_name": "ICR corr"}</t>
+          <t>{"input_names": ["Рост реального ВВП", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Хлорид калия (CFR Ю-В Азия)", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)"], "target_value": 7.73, "output_name": "ICR corr", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -27733,7 +27733,7 @@
       </c>
       <c r="J219" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент цены", "Хлорид калия (CFR Ю-В Азия)", "Ставка налога на прибыль организаций", "Ключевая ставка на конец года (eop)", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)"], "target_value": 340, "output_name": "Амортизация"}</t>
+          <t>{"input_names": ["Коэффициент цены", "Хлорид калия (CFR Ю-В Азия)", "Ставка налога на прибыль организаций", "Ключевая ставка на конец года (eop)", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)"], "target_value": 340, "output_name": "Амортизация", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -27779,7 +27779,7 @@
       </c>
       <c r="J220" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Медь (London Metals Exchange)", "Коэффициент капитальных вложений", "Нефть марки Urals"], "target_value": -260, "output_name": "Чистый денежный поток за период (NCF)"}</t>
+          <t>{"input_names": ["Медь (London Metals Exchange)", "Коэффициент капитальных вложений", "Нефть марки Urals"], "target_value": -260, "output_name": "Чистый денежный поток за период (NCF)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -27825,7 +27825,7 @@
       </c>
       <c r="J221" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Нефть марки Brent", "Никель (London Metals Exchange)", "Цена на природный газ на хабе TTF", "Цена урана"], "target_value": 140, "output_name": "Проценты к уплате"}</t>
+          <t>{"input_names": ["Нефть марки Brent", "Никель (London Metals Exchange)", "Цена на природный газ на хабе TTF", "Цена урана"], "target_value": 140, "output_name": "Проценты к уплате", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -27871,7 +27871,7 @@
       </c>
       <c r="J222" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ключевая ставка на конец года (eop)", "Нефть марки Urals", "Цена урана"], "target_value": 0.8, "output_name": "Net Debt/EBITDA (LTM)"}</t>
+          <t>{"input_names": ["Ключевая ставка на конец года (eop)", "Нефть марки Urals", "Цена урана"], "target_value": 0.8, "output_name": "Net Debt/EBITDA (LTM)", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -27917,7 +27917,7 @@
       </c>
       <c r="J223" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Курс рубля к EUR в конце года (eop EUR/RUB)", "Ключевая ставка на конец года (eop)", "Никель (London Metals Exchange)"], "target_value": 16.6, "output_name": "ISCR (LTM)"}</t>
+          <t>{"input_names": ["Курс рубля к EUR в конце года (eop EUR/RUB)", "Ключевая ставка на конец года (eop)", "Никель (London Metals Exchange)"], "target_value": 16.6, "output_name": "ISCR (LTM)", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -27963,7 +27963,7 @@
       </c>
       <c r="J224" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Нефть марки Urals", "Коэффициент цены", "ECB policy rate (Main Refinancing Operations rate)", "Метанол"], "target_value": 0.9, "output_name": "Debt/EBITDA (LTM)"}</t>
+          <t>{"input_names": ["Нефть марки Urals", "Коэффициент цены", "ECB policy rate (Main Refinancing Operations rate)", "Метанол"], "target_value": 0.9, "output_name": "Debt/EBITDA (LTM)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -28009,7 +28009,7 @@
       </c>
       <c r="J225" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ставка Libor 3m", "Цена на природный газ на хабе TTF", "Этилен, CFR Китай", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)"], "target_value": 16.05, "output_name": "ICR corr (LTM)"}</t>
+          <t>{"input_names": ["Ставка Libor 3m", "Цена на природный газ на хабе TTF", "Этилен, CFR Китай", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)"], "target_value": 16.05, "output_name": "ICR corr (LTM)", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -28055,7 +28055,7 @@
       </c>
       <c r="J226" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Цена на природный газ на хабе Henry Hub", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Этилен, CFR Китай"], "target_value": 1600, "output_name": "Чистый долг (Net Debt)"}</t>
+          <t>{"input_names": ["Цена на природный газ на хабе Henry Hub", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Этилен, CFR Китай"], "target_value": 1600, "output_name": "Чистый долг (Net Debt)", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -28101,7 +28101,7 @@
       </c>
       <c r="J227" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент объема", "Метанол", "Карбамид (FOB Южный)"], "target_value": 0.235, "output_name": "Рентабельность EBITDA (LTM)"}</t>
+          <t>{"input_names": ["Коэффициент объема", "Метанол", "Карбамид (FOB Южный)"], "target_value": 0.235, "output_name": "Рентабельность EBITDA (LTM)", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -28147,7 +28147,7 @@
       </c>
       <c r="J228" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент цены", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Этилен, CFR Китай", "Коэффициент удельных расходов"], "target_value": 7.74, "output_name": "Коэффициент покрытия процентов в i-ом периоде (ISCR)"}</t>
+          <t>{"input_names": ["Коэффициент цены", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Этилен, CFR Китай", "Коэффициент удельных расходов"], "target_value": 7.74, "output_name": "Коэффициент покрытия процентов в i-ом периоде (ISCR)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -28193,7 +28193,7 @@
       </c>
       <c r="J229" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Коэффициент капитальных вложений", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Аммиак (FOB Черное море)"], "target_value": 15.86, "output_name": "ICR corr"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Коэффициент капитальных вложений", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Аммиак (FOB Черное море)"], "target_value": 15.86, "output_name": "ICR corr", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -28239,7 +28239,7 @@
       </c>
       <c r="J230" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Ставка налога на прибыль организаций", "Курс рубля к EUR в конце года (eop EUR/RUB)"], "target_value": 1200, "output_name": "Остаток денежных средств на конец периода"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Ставка налога на прибыль организаций", "Курс рубля к EUR в конце года (eop EUR/RUB)"], "target_value": 1200, "output_name": "Остаток денежных средств на конец периода", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -28285,7 +28285,7 @@
       </c>
       <c r="J231" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Ставка Euribor 3m", "Нефть марки Brent"], "target_value": 100, "output_name": "Обслуживание долга (Debt Service)"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Ставка Euribor 3m", "Нефть марки Brent"], "target_value": 100, "output_name": "Обслуживание долга (Debt Service)", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -28331,7 +28331,7 @@
       </c>
       <c r="J232" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Курс рубля к EUR в конце года (eop EUR/RUB)", "Коэффициент цены", "Никель (London Metals Exchange)", "Цена на природный газ на хабе Henry Hub"], "target_value": 4.58, "output_name": "ICR corr (LTM)"}</t>
+          <t>{"input_names": ["Курс рубля к EUR в конце года (eop EUR/RUB)", "Коэффициент цены", "Никель (London Metals Exchange)", "Цена на природный газ на хабе Henry Hub"], "target_value": 4.58, "output_name": "ICR corr (LTM)", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -28377,7 +28377,7 @@
       </c>
       <c r="J233" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Средний за период курс рубля к доллару США (av USD/RUB)", "Ставка Euribor 3m", "Аммиак (FOB Черное море)", "Метанол"], "target_value": 7.3, "output_name": "ICR corr (LTM)"}</t>
+          <t>{"input_names": ["Средний за период курс рубля к доллару США (av USD/RUB)", "Ставка Euribor 3m", "Аммиак (FOB Черное море)", "Метанол"], "target_value": 7.3, "output_name": "ICR corr (LTM)", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -28423,7 +28423,7 @@
       </c>
       <c r="J234" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Хлорид калия (CFR Ю-В Азия)", "ECB policy rate (Main Refinancing Operations rate)", "Нефть марки Brent"], "target_value": 6.66, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)"}</t>
+          <t>{"input_names": ["Хлорид калия (CFR Ю-В Азия)", "ECB policy rate (Main Refinancing Operations rate)", "Нефть марки Brent"], "target_value": 6.66, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -28469,7 +28469,7 @@
       </c>
       <c r="J235" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Этилен, CFR Китай", "Коэффициент цены"], "target_value": 210, "output_name": "Сумма капитальных затрат (CAPEX)"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Этилен, CFR Китай", "Коэффициент цены"], "target_value": 210, "output_name": "Сумма капитальных затрат (CAPEX)", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -28515,7 +28515,7 @@
       </c>
       <c r="J236" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Метанол", "Коэффициент удельных расходов", "Медь (London Metals Exchange)"], "target_value": 10.43, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)"}</t>
+          <t>{"input_names": ["Метанол", "Коэффициент удельных расходов", "Медь (London Metals Exchange)"], "target_value": 10.43, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -28561,7 +28561,7 @@
       </c>
       <c r="J237" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Курс рубля к доллару США в конце года (eop USD/RUB)", "Ставка налога на прибыль организаций", "Рост реального ВВП", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)"], "target_value": 1250, "output_name": "EBITDA (LTM)"}</t>
+          <t>{"input_names": ["Курс рубля к доллару США в конце года (eop USD/RUB)", "Ставка налога на прибыль организаций", "Рост реального ВВП", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)"], "target_value": 1250, "output_name": "EBITDA (LTM)", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -28607,7 +28607,7 @@
       </c>
       <c r="J238" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ставка налога на прибыль организаций", "Коэффициент удельных расходов", "Никель (London Metals Exchange)", "Ставка Euribor 3m", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)"], "target_value": 3.81, "output_name": "Минимальный годичный DSCR"}</t>
+          <t>{"input_names": ["Ставка налога на прибыль организаций", "Коэффициент удельных расходов", "Никель (London Metals Exchange)", "Ставка Euribor 3m", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)"], "target_value": 3.81, "output_name": "Минимальный годичный DSCR", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -28653,7 +28653,7 @@
       </c>
       <c r="J239" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент объема", "Хлорид калия (CFR Ю-В Азия)", "Коэффициент цены"], "target_value": 1700, "output_name": "Остаток денежных средств на конец периода"}</t>
+          <t>{"input_names": ["Коэффициент объема", "Хлорид калия (CFR Ю-В Азия)", "Коэффициент цены"], "target_value": 1700, "output_name": "Остаток денежных средств на конец периода", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -28699,7 +28699,7 @@
       </c>
       <c r="J240" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Курс рубля к доллару США в конце года (eop USD/RUB)", "Рост реального ВВП", "Hard Coking Coal (FOB Australia)", "Этилен, CFR Китай", "Метанол"], "target_value": 2050, "output_name": "Остаток денежных средств на конец периода"}</t>
+          <t>{"input_names": ["Курс рубля к доллару США в конце года (eop USD/RUB)", "Рост реального ВВП", "Hard Coking Coal (FOB Australia)", "Этилен, CFR Китай", "Метанол"], "target_value": 2050, "output_name": "Остаток денежных средств на конец периода", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -28745,7 +28745,7 @@
       </c>
       <c r="J241" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Бензол, CFR Япония", "Цена на природный газ на хабе Henry Hub", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)"], "target_value": 800, "output_name": "EBITDA"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Бензол, CFR Япония", "Цена на природный газ на хабе Henry Hub", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)"], "target_value": 800, "output_name": "EBITDA", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -28791,7 +28791,7 @@
       </c>
       <c r="J242" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "ECB policy rate (Main Refinancing Operations rate)", "Бензол, CFR Япония", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)"], "target_value": 4450, "output_name": "Выручка"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "ECB policy rate (Main Refinancing Operations rate)", "Бензол, CFR Япония", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)"], "target_value": 4450, "output_name": "Выручка", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -28837,7 +28837,7 @@
       </c>
       <c r="J243" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Медь (London Metals Exchange)", "Этилен, CFR Китай", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": 1.7, "output_name": "Debt/EBITDA"}</t>
+          <t>{"input_names": ["Медь (London Metals Exchange)", "Этилен, CFR Китай", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": 1.7, "output_name": "Debt/EBITDA", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -28883,7 +28883,7 @@
       </c>
       <c r="J244" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент постоянных расходов", "Рост реального ВВП", "Коэффициент капитальных вложений", "Ставка Libor 3m"], "target_value": 3.62, "output_name": "Минимальный годичный DSCR"}</t>
+          <t>{"input_names": ["Коэффициент постоянных расходов", "Рост реального ВВП", "Коэффициент капитальных вложений", "Ставка Libor 3m"], "target_value": 3.62, "output_name": "Минимальный годичный DSCR", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -28929,7 +28929,7 @@
       </c>
       <c r="J245" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Медь (London Metals Exchange)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Никель (London Metals Exchange)", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Алюминий (London Metals Exchange, без премии)"], "target_value": 1150, "output_name": "Остаток денежных средств на конец периода"}</t>
+          <t>{"input_names": ["Медь (London Metals Exchange)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Никель (London Metals Exchange)", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Алюминий (London Metals Exchange, без премии)"], "target_value": 1150, "output_name": "Остаток денежных средств на конец периода", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -28975,7 +28975,7 @@
       </c>
       <c r="J246" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Этилен, CFR Китай", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Цена на природный газ на хабе TTF", "Карбамид (FOB Южный)"], "target_value": 10.78, "output_name": "ICR corr"}</t>
+          <t>{"input_names": ["Этилен, CFR Китай", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Цена на природный газ на хабе TTF", "Карбамид (FOB Южный)"], "target_value": 10.78, "output_name": "ICR corr", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -29021,7 +29021,7 @@
       </c>
       <c r="J247" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Железная руда (Iron Ore 62%, CFR China)", "Ставка налога на прибыль организаций", "Метанол"], "target_value": 8.21, "output_name": "ICR corr"}</t>
+          <t>{"input_names": ["Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Железная руда (Iron Ore 62%, CFR China)", "Ставка налога на прибыль организаций", "Метанол"], "target_value": 8.21, "output_name": "ICR corr", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -29067,7 +29067,7 @@
       </c>
       <c r="J248" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Золото (London Metals Exchange)", "Коэффициент постоянных расходов", "Этилен, CFR Китай", "Коэффициент капитальных вложений"], "target_value": 650, "output_name": "Свободный денежный поток (FCFF)"}</t>
+          <t>{"input_names": ["Золото (London Metals Exchange)", "Коэффициент постоянных расходов", "Этилен, CFR Китай", "Коэффициент капитальных вложений"], "target_value": 650, "output_name": "Свободный денежный поток (FCFF)", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -29113,7 +29113,7 @@
       </c>
       <c r="J249" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ставка Libor 3m", "Нефть марки Urals", "Нефть марки Brent"], "target_value": 300, "output_name": "Амортизация"}</t>
+          <t>{"input_names": ["Ставка Libor 3m", "Нефть марки Urals", "Нефть марки Brent"], "target_value": 300, "output_name": "Амортизация", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -29159,7 +29159,7 @@
       </c>
       <c r="J250" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Этилен, CFR Китай", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Нефть марки Urals", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)"], "target_value": 3650, "output_name": "Выручка (LTM)"}</t>
+          <t>{"input_names": ["Этилен, CFR Китай", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Нефть марки Urals", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)"], "target_value": 3650, "output_name": "Выручка (LTM)", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -29205,7 +29205,7 @@
       </c>
       <c r="J251" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Цена на природный газ на хабе TTF", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Железная руда (Iron Ore 62%, CFR China)"], "target_value": 0.193, "output_name": "Рентабельность EBITDA (LTM)"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Цена на природный газ на хабе TTF", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Железная руда (Iron Ore 62%, CFR China)"], "target_value": 0.193, "output_name": "Рентабельность EBITDA (LTM)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -29251,7 +29251,7 @@
       </c>
       <c r="J252" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент цены", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)"], "target_value": 2.95, "output_name": "Минимальный годичный ISCR"}</t>
+          <t>{"input_names": ["Коэффициент цены", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)"], "target_value": 2.95, "output_name": "Минимальный годичный ISCR", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -29297,7 +29297,7 @@
       </c>
       <c r="J253" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Золото (London Metals Exchange)", "Этилен, CFR Китай", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Коэффициент капитальных вложений"], "target_value": 150, "output_name": "Сумма капитальных затрат (CAPEX)"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Золото (London Metals Exchange)", "Этилен, CFR Китай", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Коэффициент капитальных вложений"], "target_value": 150, "output_name": "Сумма капитальных затрат (CAPEX)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -29343,7 +29343,7 @@
       </c>
       <c r="J254" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Метанол", "Медь (London Metals Exchange)", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": 12.3, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)"}</t>
+          <t>{"input_names": ["Метанол", "Медь (London Metals Exchange)", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": 12.3, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -29389,7 +29389,7 @@
       </c>
       <c r="J255" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Цена урана", "Ставка налога на прибыль организаций"], "target_value": 23.27, "output_name": "Коэффициент покрытия процентов в i-ом периоде (ICR)"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Цена урана", "Ставка налога на прибыль организаций"], "target_value": 23.27, "output_name": "Коэффициент покрытия процентов в i-ом периоде (ICR)", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -29435,7 +29435,7 @@
       </c>
       <c r="J256" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ставка налога на прибыль организаций", "Коэффициент капитальных вложений", "Hard Coking Coal (FOB Australia)", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Железная руда (Iron Ore 62%, CFR China)"], "target_value": 1.8, "output_name": "Net Debt/EBITDA (LTM)"}</t>
+          <t>{"input_names": ["Ставка налога на прибыль организаций", "Коэффициент капитальных вложений", "Hard Coking Coal (FOB Australia)", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Железная руда (Iron Ore 62%, CFR China)"], "target_value": 1.8, "output_name": "Net Debt/EBITDA (LTM)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -29481,7 +29481,7 @@
       </c>
       <c r="J257" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент постоянных расходов", "Ставка налога на прибыль организаций", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)"], "target_value": 6.08, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)"}</t>
+          <t>{"input_names": ["Коэффициент постоянных расходов", "Ставка налога на прибыль организаций", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)"], "target_value": 6.08, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -29527,7 +29527,7 @@
       </c>
       <c r="J258" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ставка Libor 3m", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)"], "target_value": 700, "output_name": "Денежные средства, доступные для обслуживания долга (CFADS)"}</t>
+          <t>{"input_names": ["Ставка Libor 3m", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)"], "target_value": 700, "output_name": "Денежные средства, доступные для обслуживания долга (CFADS)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -29573,7 +29573,7 @@
       </c>
       <c r="J259" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Золото (London Metals Exchange)", "Hard Coking Coal (FOB Australia)", "Цена на природный газ на хабе TTF", "ECB policy rate (Main Refinancing Operations rate)"], "target_value": 3.41, "output_name": "Минимальный годичный DSCR"}</t>
+          <t>{"input_names": ["Золото (London Metals Exchange)", "Hard Coking Coal (FOB Australia)", "Цена на природный газ на хабе TTF", "ECB policy rate (Main Refinancing Operations rate)"], "target_value": 3.41, "output_name": "Минимальный годичный DSCR", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -29619,7 +29619,7 @@
       </c>
       <c r="J260" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Нефть марки Urals", "Никель (London Metals Exchange)", "Золото (London Metals Exchange)", "Ставка налога на прибыль организаций"], "target_value": 120, "output_name": "Обслуживание долга (Debt Service)"}</t>
+          <t>{"input_names": ["Нефть марки Urals", "Никель (London Metals Exchange)", "Золото (London Metals Exchange)", "Ставка налога на прибыль организаций"], "target_value": 120, "output_name": "Обслуживание долга (Debt Service)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -29665,7 +29665,7 @@
       </c>
       <c r="J261" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Бензол, CFR Япония", "Ставка Libor 3m", "Железная руда (Iron Ore 62%, CFR China)", "ECB policy rate (Main Refinancing Operations rate)", "Цена на природный газ на хабе Henry Hub"], "target_value": -900, "output_name": "Чистый долг (Net Debt)"}</t>
+          <t>{"input_names": ["Бензол, CFR Япония", "Ставка Libor 3m", "Железная руда (Iron Ore 62%, CFR China)", "ECB policy rate (Main Refinancing Operations rate)", "Цена на природный газ на хабе Henry Hub"], "target_value": -900, "output_name": "Чистый долг (Net Debt)", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -29711,7 +29711,7 @@
       </c>
       <c r="J262" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ключевая ставка на конец года (eop)", "Хлорид калия (CFR Ю-В Азия)", "Нефть марки Urals", "Hard Coking Coal (FOB Australia)"], "target_value": 6.65, "output_name": "ICR corr"}</t>
+          <t>{"input_names": ["Ключевая ставка на конец года (eop)", "Хлорид калия (CFR Ю-В Азия)", "Нефть марки Urals", "Hard Coking Coal (FOB Australia)"], "target_value": 6.65, "output_name": "ICR corr", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -29757,7 +29757,7 @@
       </c>
       <c r="J263" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Hard Coking Coal (FOB Australia)", "Коэффициент объема", "Коэффициент удельных расходов", "Ставка налога на прибыль организаций", "Аммиак (FOB Черное море)"], "target_value": 0.132, "output_name": "Рентабельность чистой прибыли"}</t>
+          <t>{"input_names": ["Hard Coking Coal (FOB Australia)", "Коэффициент объема", "Коэффициент удельных расходов", "Ставка налога на прибыль организаций", "Аммиак (FOB Черное море)"], "target_value": 0.132, "output_name": "Рентабельность чистой прибыли", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -29803,7 +29803,7 @@
       </c>
       <c r="J264" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Hard Coking Coal (FOB Australia)", "Ключевая ставка на конец года (eop)", "Ставка Libor 3m"], "target_value": 5250, "output_name": "Выручка (LTM)"}</t>
+          <t>{"input_names": ["Hard Coking Coal (FOB Australia)", "Ключевая ставка на конец года (eop)", "Ставка Libor 3m"], "target_value": 5250, "output_name": "Выручка (LTM)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -29849,7 +29849,7 @@
       </c>
       <c r="J265" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ставка налога на прибыль организаций", "Курс рубля к доллару США в конце года (eop USD/RUB)", "Цена на природный газ на хабе TTF", "Коэффициент капитальных вложений", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": 0.112, "output_name": "Рентабельность чистой прибыли"}</t>
+          <t>{"input_names": ["Ставка налога на прибыль организаций", "Курс рубля к доллару США в конце года (eop USD/RUB)", "Цена на природный газ на хабе TTF", "Коэффициент капитальных вложений", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": 0.112, "output_name": "Рентабельность чистой прибыли", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -29895,7 +29895,7 @@
       </c>
       <c r="J266" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент удельных расходов", "Цена урана", "Бензол, CFR Япония", "Коэффициент капитальных вложений"], "target_value": 850, "output_name": "EBITDA"}</t>
+          <t>{"input_names": ["Коэффициент удельных расходов", "Цена урана", "Бензол, CFR Япония", "Коэффициент капитальных вложений"], "target_value": 850, "output_name": "EBITDA", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -29941,7 +29941,7 @@
       </c>
       <c r="J267" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Медь (London Metals Exchange)", "Метанол", "Ставка налога на прибыль организаций"], "target_value": 1300, "output_name": "Долг (Debt)"}</t>
+          <t>{"input_names": ["Медь (London Metals Exchange)", "Метанол", "Ставка налога на прибыль организаций"], "target_value": 1300, "output_name": "Долг (Debt)", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -29987,7 +29987,7 @@
       </c>
       <c r="J268" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ключевая ставка на конец года (eop)", "Средний за период курс рубля к доллару США (av USD/RUB)", "Аммиак (FOB Черное море)"], "target_value": 400, "output_name": "Чистая прибыль"}</t>
+          <t>{"input_names": ["Ключевая ставка на конец года (eop)", "Средний за период курс рубля к доллару США (av USD/RUB)", "Аммиак (FOB Черное море)"], "target_value": 400, "output_name": "Чистая прибыль", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -30033,7 +30033,7 @@
       </c>
       <c r="J269" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Курс рубля к EUR в конце года (eop EUR/RUB)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Коэффициент капитальных вложений", "Коэффициент удельных расходов", "Цена урана"], "target_value": 10.79, "output_name": "ICR corr"}</t>
+          <t>{"input_names": ["Курс рубля к EUR в конце года (eop EUR/RUB)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Коэффициент капитальных вложений", "Коэффициент удельных расходов", "Цена урана"], "target_value": 10.79, "output_name": "ICR corr", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -30079,7 +30079,7 @@
       </c>
       <c r="J270" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Золото (London Metals Exchange)", "Нефть марки Urals", "Аммиак (FOB Черное море)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)"], "target_value": 5.35, "output_name": "ICR corr (LTM)"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Золото (London Metals Exchange)", "Нефть марки Urals", "Аммиак (FOB Черное море)", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)"], "target_value": 5.35, "output_name": "ICR corr (LTM)", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -30125,7 +30125,7 @@
       </c>
       <c r="J271" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ставка Euribor 3m", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "ECB policy rate (Main Refinancing Operations rate)", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": 170, "output_name": "Сумма капитальных затрат (CAPEX)"}</t>
+          <t>{"input_names": ["Ставка Euribor 3m", "Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "ECB policy rate (Main Refinancing Operations rate)", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": 170, "output_name": "Сумма капитальных затрат (CAPEX)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -30171,7 +30171,7 @@
       </c>
       <c r="J272" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Цена урана", "Медь (London Metals Exchange)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)"], "target_value": 0.2, "output_name": "Рентабельность EBITDA (LTM)"}</t>
+          <t>{"input_names": ["Цена урана", "Медь (London Metals Exchange)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)"], "target_value": 0.2, "output_name": "Рентабельность EBITDA (LTM)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -30217,7 +30217,7 @@
       </c>
       <c r="J273" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Алюминий (London Metals Exchange, без премии)", "Карбамид (FOB Южный)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Курс рубля к доллару США в конце года (eop USD/RUB)", "Ставка налога на прибыль организаций"], "target_value": 750, "output_name": "Денежные потоки от текущих операций (CFO)"}</t>
+          <t>{"input_names": ["Алюминий (London Metals Exchange, без премии)", "Карбамид (FOB Южный)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Курс рубля к доллару США в конце года (eop USD/RUB)", "Ставка налога на прибыль организаций"], "target_value": 750, "output_name": "Денежные потоки от текущих операций (CFO)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -30263,7 +30263,7 @@
       </c>
       <c r="J274" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент цены", "Коэффициент капитальных вложений", "Медь (London Metals Exchange)", "Железная руда (Iron Ore 62%, CFR China)", "Ставка Libor 3m"], "target_value": 0.87, "output_name": "Net Debt/EBITDA"}</t>
+          <t>{"input_names": ["Коэффициент цены", "Коэффициент капитальных вложений", "Медь (London Metals Exchange)", "Железная руда (Iron Ore 62%, CFR China)", "Ставка Libor 3m"], "target_value": 0.87, "output_name": "Net Debt/EBITDA", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -30309,7 +30309,7 @@
       </c>
       <c r="J275" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ставка Euribor 3m", "Коэффициент цены", "Бензол, CFR Япония"], "target_value": 6.46, "output_name": "Коэффициент покрытия процентов в i-ом периоде (ISCR)"}</t>
+          <t>{"input_names": ["Ставка Euribor 3m", "Коэффициент цены", "Бензол, CFR Япония"], "target_value": 6.46, "output_name": "Коэффициент покрытия процентов в i-ом периоде (ISCR)", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -30355,7 +30355,7 @@
       </c>
       <c r="J276" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ключевая ставка на конец года (eop)", "Никель (London Metals Exchange)", "Золото (London Metals Exchange)"], "target_value": 850, "output_name": "EBITDA"}</t>
+          <t>{"input_names": ["Ключевая ставка на конец года (eop)", "Никель (London Metals Exchange)", "Золото (London Metals Exchange)"], "target_value": 850, "output_name": "EBITDA", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -30401,7 +30401,7 @@
       </c>
       <c r="J277" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Этилен, CFR Китай", "Коэффициент цены", "ECB policy rate (Main Refinancing Operations rate)", "Коэффициент постоянных расходов", "Коэффициент удельных расходов"], "target_value": 65, "output_name": "Обслуживание долга (Debt Service)"}</t>
+          <t>{"input_names": ["Этилен, CFR Китай", "Коэффициент цены", "ECB policy rate (Main Refinancing Operations rate)", "Коэффициент постоянных расходов", "Коэффициент удельных расходов"], "target_value": 65, "output_name": "Обслуживание долга (Debt Service)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -30447,7 +30447,7 @@
       </c>
       <c r="J278" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Курс рубля к доллару США в конце года (eop USD/RUB)", "ECB policy rate (Main Refinancing Operations rate)", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": 480, "output_name": "Чистый денежный поток за период (NCF)"}</t>
+          <t>{"input_names": ["Курс рубля к доллару США в конце года (eop USD/RUB)", "ECB policy rate (Main Refinancing Operations rate)", "Средний за период курс рубля к доллару США (av USD/RUB)"], "target_value": 480, "output_name": "Чистый денежный поток за период (NCF)", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -30493,7 +30493,7 @@
       </c>
       <c r="J279" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["ECB policy rate (Main Refinancing Operations rate)", "Ключевая ставка на конец года (eop)", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Ставка Libor 3m"], "target_value": -30, "output_name": "Чистый долг (Net Debt)"}</t>
+          <t>{"input_names": ["ECB policy rate (Main Refinancing Operations rate)", "Ключевая ставка на конец года (eop)", "Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Ставка Libor 3m"], "target_value": -30, "output_name": "Чистый долг (Net Debt)", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -30539,7 +30539,7 @@
       </c>
       <c r="J280" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Алюминий (London Metals Exchange, без премии)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Медь (London Metals Exchange)"], "target_value": 105, "output_name": "Обслуживание долга (Debt Service)"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Алюминий (London Metals Exchange, без премии)", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Медь (London Metals Exchange)"], "target_value": 105, "output_name": "Обслуживание долга (Debt Service)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -30585,7 +30585,7 @@
       </c>
       <c r="J281" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Аммиак (FOB Черное море)", "Золото (London Metals Exchange)", "Хлорид калия (CFR Ю-В Азия)"], "target_value": 1000, "output_name": "Денежные средства, доступные для обслуживания долга (CFADS)"}</t>
+          <t>{"input_names": ["Аммиак (FOB Черное море)", "Золото (London Metals Exchange)", "Хлорид калия (CFR Ю-В Азия)"], "target_value": 1000, "output_name": "Денежные средства, доступные для обслуживания долга (CFADS)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -30631,7 +30631,7 @@
       </c>
       <c r="J282" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Аммиак (FOB Черное море)", "Цена на природный газ на хабе TTF", "Этилен, CFR Китай"], "target_value": 1050, "output_name": "Чистый долг (Net Debt)"}</t>
+          <t>{"input_names": ["Аммиак (FOB Черное море)", "Цена на природный газ на хабе TTF", "Этилен, CFR Китай"], "target_value": 1050, "output_name": "Чистый долг (Net Debt)", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -30677,7 +30677,7 @@
       </c>
       <c r="J283" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент объема", "Коэффициент капитальных вложений", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Карбамид (FOB Южный)", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)"], "target_value": 6.76, "output_name": "DSCR (LTM)"}</t>
+          <t>{"input_names": ["Коэффициент объема", "Коэффициент капитальных вложений", "Инфляция - Рост индекса потребительских цен (RUB, eop CPI)", "Карбамид (FOB Южный)", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)"], "target_value": 6.76, "output_name": "DSCR (LTM)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -30723,7 +30723,7 @@
       </c>
       <c r="J284" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ставка Euribor 3m", "Бензол, CFR Япония", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Железная руда (Iron Ore 62%, CFR China)"], "target_value": 170, "output_name": "Обслуживание долга (Debt Service)"}</t>
+          <t>{"input_names": ["Ставка Euribor 3m", "Бензол, CFR Япония", "Стоимость квот на CO2 в EU ETS (Emissions Trading System)", "Железная руда (Iron Ore 62%, CFR China)"], "target_value": 170, "output_name": "Обслуживание долга (Debt Service)", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -30769,7 +30769,7 @@
       </c>
       <c r="J285" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Hard Coking Coal (FOB Australia)", "Алюминий (London Metals Exchange, без премии)", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Нефть марки Brent"], "target_value": 8.19, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)"}</t>
+          <t>{"input_names": ["Hard Coking Coal (FOB Australia)", "Алюминий (London Metals Exchange, без премии)", "Инфляция - Рост индекса цен производителей (RUB, eop PPI)", "Нефть марки Brent"], "target_value": 8.19, "output_name": "Коэффициент покрытия долга в i-ом периоде (DSCR)", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -30815,7 +30815,7 @@
       </c>
       <c r="J286" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Алюминий (London Metals Exchange, без премии)", "Цена урана", "Золото (London Metals Exchange)", "Бензол, CFR Япония"], "target_value": 10.0, "output_name": "Коэффициент покрытия процентов в i-ом периоде (ISCR)"}</t>
+          <t>{"input_names": ["Алюминий (London Metals Exchange, без премии)", "Цена урана", "Золото (London Metals Exchange)", "Бензол, CFR Япония"], "target_value": 10.0, "output_name": "Коэффициент покрытия процентов в i-ом периоде (ISCR)", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -30861,7 +30861,7 @@
       </c>
       <c r="J287" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Золото (London Metals Exchange)", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Никель (London Metals Exchange)"], "target_value": 0.105, "output_name": "Рентабельность чистой прибыли"}</t>
+          <t>{"input_names": ["Золото (London Metals Exchange)", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Никель (London Metals Exchange)"], "target_value": 0.105, "output_name": "Рентабельность чистой прибыли", "output_year": 2026}</t>
         </is>
       </c>
     </row>
@@ -30907,7 +30907,7 @@
       </c>
       <c r="J288" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Коэффициент объема", "Медь (London Metals Exchange)", "Железная руда (Iron Ore 62%, CFR China)", "Курс рубля к доллару США в конце года (eop USD/RUB)", "Hard Coking Coal (FOB Australia)"], "target_value": 7.66, "output_name": "Коэффициент покрытия процентов в i-ом периоде (ISCR)"}</t>
+          <t>{"input_names": ["Коэффициент объема", "Медь (London Metals Exchange)", "Железная руда (Iron Ore 62%, CFR China)", "Курс рубля к доллару США в конце года (eop USD/RUB)", "Hard Coking Coal (FOB Australia)"], "target_value": 7.66, "output_name": "Коэффициент покрытия процентов в i-ом периоде (ISCR)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -30953,7 +30953,7 @@
       </c>
       <c r="J289" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ключевая ставка на конец года (eop)", "Цена на природный газ на хабе Henry Hub", "Рост реального ВВП", "Коэффициент цены"], "target_value": 0.261, "output_name": "Рентабельность EBITDA"}</t>
+          <t>{"input_names": ["Ключевая ставка на конец года (eop)", "Цена на природный газ на хабе Henry Hub", "Рост реального ВВП", "Коэффициент цены"], "target_value": 0.261, "output_name": "Рентабельность EBITDA", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -30999,7 +30999,7 @@
       </c>
       <c r="J290" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Нефть марки Urals", "Коэффициент удельных расходов", "Коэффициент объема"], "target_value": 3650, "output_name": "Выручка"}</t>
+          <t>{"input_names": ["Нефть марки Urals", "Коэффициент удельных расходов", "Коэффициент объема"], "target_value": 3650, "output_name": "Выручка", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -31045,7 +31045,7 @@
       </c>
       <c r="J291" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Цена урана", "Метанол", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Алюминий (London Metals Exchange, без премии)", "Коэффициент цены"], "target_value": 0.098, "output_name": "Рентабельность чистой прибыли"}</t>
+          <t>{"input_names": ["Цена урана", "Метанол", "Курс рубля к EUR в конце года (eop EUR/RUB)", "Алюминий (London Metals Exchange, без премии)", "Коэффициент цены"], "target_value": 0.098, "output_name": "Рентабельность чистой прибыли", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -31091,7 +31091,7 @@
       </c>
       <c r="J292" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ставка Euribor 3m", "Коэффициент капитальных вложений", "Цена на природный газ на хабе Henry Hub"], "target_value": 1.48, "output_name": "Net Debt/EBITDA"}</t>
+          <t>{"input_names": ["Ставка Euribor 3m", "Коэффициент капитальных вложений", "Цена на природный газ на хабе Henry Hub"], "target_value": 1.48, "output_name": "Net Debt/EBITDA", "output_year": 2025}</t>
         </is>
       </c>
     </row>
@@ -31137,7 +31137,7 @@
       </c>
       <c r="J293" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Хлорид калия (CFR Ю-В Азия)", "Цена на природный газ на хабе Henry Hub", "Коэффициент удельных расходов", "Медь (London Metals Exchange)"], "target_value": -310, "output_name": "Денежные потоки от финансовых операций (CFF)"}</t>
+          <t>{"input_names": ["Хлорид калия (CFR Ю-В Азия)", "Цена на природный газ на хабе Henry Hub", "Коэффициент удельных расходов", "Медь (London Metals Exchange)"], "target_value": -310, "output_name": "Денежные потоки от финансовых операций (CFF)", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -31183,7 +31183,7 @@
       </c>
       <c r="J294" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ставка Libor 3m", "Ключевая ставка на конец года (eop)", "Карбамид (FOB Южный)", "Ставка налога на прибыль организаций"], "target_value": 1250, "output_name": "EBITDA (LTM)"}</t>
+          <t>{"input_names": ["Ставка Libor 3m", "Ключевая ставка на конец года (eop)", "Карбамид (FOB Южный)", "Ставка налога на прибыль организаций"], "target_value": 1250, "output_name": "EBITDA (LTM)", "output_year": 2029}</t>
         </is>
       </c>
     </row>
@@ -31229,7 +31229,7 @@
       </c>
       <c r="J295" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Медь (London Metals Exchange)", "Этилен, CFR Китай"], "target_value": 60, "output_name": "Обслуживание долга (Debt Service)"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в Еврозоне (EUR, eop CPI)", "Медь (London Metals Exchange)", "Этилен, CFR Китай"], "target_value": 60, "output_name": "Обслуживание долга (Debt Service)", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -31275,7 +31275,7 @@
       </c>
       <c r="J296" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Ключевая ставка на конец года (eop)", "Этилен, CFR Китай"], "target_value": 640, "output_name": "Чистая прибыль"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса цен производителей в США, в долларах США (USD, eop PPI)", "Ключевая ставка на конец года (eop)", "Этилен, CFR Китай"], "target_value": 640, "output_name": "Чистая прибыль", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -31321,7 +31321,7 @@
       </c>
       <c r="J297" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Курс рубля к EUR в конце года (eop EUR/RUB)", "Медь (London Metals Exchange)", "Бензол, CFR Япония", "Золото (London Metals Exchange)", "Карбамид (FOB Южный)"], "target_value": 900, "output_name": "Денежные средства, доступные для обслуживания долга (CFADS)"}</t>
+          <t>{"input_names": ["Курс рубля к EUR в конце года (eop EUR/RUB)", "Медь (London Metals Exchange)", "Бензол, CFR Япония", "Золото (London Metals Exchange)", "Карбамид (FOB Южный)"], "target_value": 900, "output_name": "Денежные средства, доступные для обслуживания долга (CFADS)", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -31367,7 +31367,7 @@
       </c>
       <c r="J298" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Ставка Libor 3m", "Алюминий (London Metals Exchange, без премии)", "Средний за период курс рубля к доллару США (av USD/RUB)", "Коэффициент капитальных вложений"], "target_value": 0.144, "output_name": "Рентабельность чистой прибыли"}</t>
+          <t>{"input_names": ["Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Ставка Libor 3m", "Алюминий (London Metals Exchange, без премии)", "Средний за период курс рубля к доллару США (av USD/RUB)", "Коэффициент капитальных вложений"], "target_value": 0.144, "output_name": "Рентабельность чистой прибыли", "output_year": 2030}</t>
         </is>
       </c>
     </row>
@@ -31413,7 +31413,7 @@
       </c>
       <c r="J299" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Метанол", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Алюминий (London Metals Exchange, без премии)"], "target_value": 2.24, "output_name": "Минимальный годичный DSCR"}</t>
+          <t>{"input_names": ["Метанол", "Инфляция - Рост индекса потребительских цен в США, в долларах США (USD, eop CPI)", "Алюминий (London Metals Exchange, без премии)"], "target_value": 2.24, "output_name": "Минимальный годичный DSCR", "output_year": 2028}</t>
         </is>
       </c>
     </row>
@@ -31459,7 +31459,7 @@
       </c>
       <c r="J300" s="6" t="inlineStr">
         <is>
-          <t>{"input_names": ["Аммиак (FOB Черное море)", "Никель (London Metals Exchange)", "Нефть марки Urals", "Этилен, CFR Китай", "Коэффициент цены"], "target_value": 260, "output_name": "Амортизация"}</t>
+          <t>{"input_names": ["Аммиак (FOB Черное море)", "Никель (London Metals Exchange)", "Нефть марки Urals", "Этилен, CFR Китай", "Коэффициент цены"], "target_value": 260, "output_name": "Амортизация", "output_year": 2027}</t>
         </is>
       </c>
     </row>
@@ -31505,7 +31505,7 @@
       </c>
       <c r="J301" s="8" t="inlineStr">
         <is>
-          <t>{"input_names": ["Ставка налога на прибыль организаций", "Ставка Libor 3m", "Ставка Euribor 3m"], "target_value": 6.93, "output_name": "ICR corr (LTM)"}</t>
+          <t>{"input_names": ["Ставка налога на прибыль организаций", "Ставка Libor 3m", "Ставка Euribor 3m"], "target_value": 6.93, "output_name": "ICR corr (LTM)", "output_year": 2026}</t>
         </is>
       </c>
     </row>
